--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:21:44+00:00</t>
+    <t>2024-07-01T16:22:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="823">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:22:22+00:00</t>
+    <t>2024-07-02T08:22:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,6 +689,9 @@
 </t>
   </si>
   <si>
+    <t>Optional Extensions Element</t>
+  </si>
+  <si>
     <t>The date range that this organization should be considered available.</t>
   </si>
   <si>
@@ -782,8 +785,8 @@
     <t>Period.start</t>
   </si>
   <si>
-    <t xml:space="preserve">per-1
-</t>
+    <t>ele-1
+per-1</t>
   </si>
   <si>
     <t>dateCreation</t>
@@ -5417,10 +5420,10 @@
         <v>214</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5492,7 +5495,7 @@
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>78</v>
@@ -5503,10 +5506,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5618,10 +5621,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5733,10 +5736,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5762,13 +5765,13 @@
         <v>136</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -5776,7 +5779,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>78</v>
@@ -5818,7 +5821,7 @@
         <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>89</v>
@@ -5850,10 +5853,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5876,13 +5879,13 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5933,7 +5936,7 @@
         <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -5942,7 +5945,7 @@
         <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>101</v>
@@ -5965,10 +5968,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6080,10 +6083,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6174,7 +6177,7 @@
         <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>118</v>
@@ -6186,7 +6189,7 @@
         <v>78</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>78</v>
@@ -6197,10 +6200,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6223,16 +6226,16 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6282,7 +6285,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -6291,19 +6294,19 @@
         <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>78</v>
@@ -6314,10 +6317,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6340,23 +6343,23 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R30" t="s" s="2">
         <v>78</v>
@@ -6401,7 +6404,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -6410,19 +6413,19 @@
         <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>78</v>
@@ -6433,13 +6436,13 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D31" t="s" s="2">
         <v>78</v>
@@ -6461,13 +6464,13 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6550,13 +6553,13 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D32" t="s" s="2">
         <v>78</v>
@@ -6578,13 +6581,13 @@
         <v>78</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6650,7 +6653,7 @@
         <v>118</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>78</v>
@@ -6667,13 +6670,13 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>78</v>
@@ -6695,13 +6698,13 @@
         <v>78</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6784,13 +6787,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6812,13 +6815,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6884,7 +6887,7 @@
         <v>118</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>78</v>
@@ -6901,13 +6904,13 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D35" t="s" s="2">
         <v>78</v>
@@ -6929,13 +6932,13 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7018,13 +7021,13 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>199</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>78</v>
@@ -7046,13 +7049,13 @@
         <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -7135,10 +7138,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7164,16 +7167,16 @@
         <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -7222,7 +7225,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -7254,10 +7257,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7280,17 +7283,17 @@
         <v>90</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -7327,10 +7330,10 @@
         <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>78</v>
@@ -7339,7 +7342,7 @@
         <v>116</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -7348,7 +7351,7 @@
         <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>101</v>
@@ -7357,27 +7360,27 @@
         <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="D39" t="s" s="2">
         <v>78</v>
@@ -7399,17 +7402,17 @@
         <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>78</v>
@@ -7458,7 +7461,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -7467,33 +7470,33 @@
         <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7605,10 +7608,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7722,10 +7725,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7751,16 +7754,16 @@
         <v>175</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7770,7 +7773,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7785,13 +7788,13 @@
         <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>78</v>
@@ -7809,7 +7812,7 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -7830,7 +7833,7 @@
         <v>198</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>78</v>
@@ -7841,10 +7844,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7867,19 +7870,19 @@
         <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7889,7 +7892,7 @@
         <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>78</v>
@@ -7907,10 +7910,10 @@
         <v>157</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>78</v>
@@ -7928,7 +7931,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -7946,10 +7949,10 @@
         <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>78</v>
@@ -7960,10 +7963,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7989,16 +7992,16 @@
         <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -8008,10 +8011,10 @@
         <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>78</v>
@@ -8047,7 +8050,7 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -8065,13 +8068,13 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>78</v>
@@ -8079,10 +8082,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8108,13 +8111,13 @@
         <v>103</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8128,7 +8131,7 @@
         <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>78</v>
@@ -8164,7 +8167,7 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -8182,13 +8185,13 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>78</v>
@@ -8196,10 +8199,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8222,13 +8225,13 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8279,7 +8282,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -8297,13 +8300,13 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>78</v>
@@ -8311,10 +8314,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8337,16 +8340,16 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8396,7 +8399,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -8414,13 +8417,13 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>78</v>
@@ -8428,13 +8431,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>78</v>
@@ -8456,17 +8459,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -8515,7 +8518,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -8524,33 +8527,33 @@
         <v>80</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ48" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8662,10 +8665,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8779,10 +8782,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8808,16 +8811,16 @@
         <v>175</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>78</v>
@@ -8842,13 +8845,13 @@
         <v>78</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>78</v>
@@ -8866,7 +8869,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8887,7 +8890,7 @@
         <v>198</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
@@ -8898,10 +8901,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8924,19 +8927,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8964,10 +8967,10 @@
         <v>157</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>78</v>
@@ -8985,7 +8988,7 @@
         <v>78</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -9003,10 +9006,10 @@
         <v>78</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>78</v>
@@ -9017,10 +9020,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9132,10 +9135,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9249,10 +9252,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9278,16 +9281,16 @@
         <v>153</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
@@ -9336,7 +9339,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -9354,10 +9357,10 @@
         <v>78</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>78</v>
@@ -9368,10 +9371,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9483,10 +9486,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9600,10 +9603,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9629,16 +9632,16 @@
         <v>136</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9648,7 +9651,7 @@
         <v>78</v>
       </c>
       <c r="S58" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="T58" t="s" s="2">
         <v>78</v>
@@ -9687,7 +9690,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9705,10 +9708,10 @@
         <v>78</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>78</v>
@@ -9719,10 +9722,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9748,13 +9751,13 @@
         <v>103</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9804,7 +9807,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9822,10 +9825,10 @@
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9836,10 +9839,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9865,14 +9868,14 @@
         <v>175</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9921,7 +9924,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9939,10 +9942,10 @@
         <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>78</v>
@@ -9953,10 +9956,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9982,14 +9985,14 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
@@ -10038,7 +10041,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -10056,10 +10059,10 @@
         <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>78</v>
@@ -10070,10 +10073,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10096,19 +10099,19 @@
         <v>90</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>78</v>
@@ -10157,7 +10160,7 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
@@ -10175,10 +10178,10 @@
         <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>78</v>
@@ -10189,10 +10192,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10218,16 +10221,16 @@
         <v>103</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10276,7 +10279,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -10294,10 +10297,10 @@
         <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>78</v>
@@ -10308,10 +10311,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10337,16 +10340,16 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -10356,10 +10359,10 @@
         <v>78</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>78</v>
@@ -10395,7 +10398,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -10413,13 +10416,13 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10427,10 +10430,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10456,13 +10459,13 @@
         <v>103</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10476,7 +10479,7 @@
         <v>78</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>78</v>
@@ -10512,7 +10515,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
@@ -10530,13 +10533,13 @@
         <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10544,10 +10547,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10570,13 +10573,13 @@
         <v>90</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10627,7 +10630,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -10645,13 +10648,13 @@
         <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10659,10 +10662,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10685,16 +10688,16 @@
         <v>90</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -10744,7 +10747,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>79</v>
@@ -10762,13 +10765,13 @@
         <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10776,13 +10779,13 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>78</v>
@@ -10804,17 +10807,17 @@
         <v>90</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10863,7 +10866,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10872,33 +10875,33 @@
         <v>80</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11010,10 +11013,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11127,10 +11130,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11156,16 +11159,16 @@
         <v>175</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -11190,13 +11193,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -11214,7 +11217,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -11235,7 +11238,7 @@
         <v>198</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>78</v>
@@ -11246,10 +11249,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11272,19 +11275,19 @@
         <v>90</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>78</v>
@@ -11312,10 +11315,10 @@
         <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -11333,7 +11336,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -11351,10 +11354,10 @@
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>78</v>
@@ -11365,10 +11368,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11480,10 +11483,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11597,10 +11600,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11626,16 +11629,16 @@
         <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11684,7 +11687,7 @@
         <v>78</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>79</v>
@@ -11702,10 +11705,10 @@
         <v>78</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>78</v>
@@ -11716,10 +11719,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11831,10 +11834,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11948,10 +11951,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11977,16 +11980,16 @@
         <v>136</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11996,7 +11999,7 @@
         <v>78</v>
       </c>
       <c r="S78" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="T78" t="s" s="2">
         <v>78</v>
@@ -12035,7 +12038,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -12053,10 +12056,10 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>78</v>
@@ -12067,10 +12070,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12096,13 +12099,13 @@
         <v>103</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -12152,7 +12155,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -12170,10 +12173,10 @@
         <v>78</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>78</v>
@@ -12184,10 +12187,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12213,14 +12216,14 @@
         <v>175</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>78</v>
@@ -12269,7 +12272,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -12287,10 +12290,10 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>78</v>
@@ -12301,10 +12304,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12330,14 +12333,14 @@
         <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
@@ -12386,7 +12389,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -12404,10 +12407,10 @@
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>78</v>
@@ -12418,10 +12421,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12444,19 +12447,19 @@
         <v>90</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12505,7 +12508,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -12523,10 +12526,10 @@
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>78</v>
@@ -12537,10 +12540,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12566,16 +12569,16 @@
         <v>103</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12624,7 +12627,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12642,10 +12645,10 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>78</v>
@@ -12656,10 +12659,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12685,16 +12688,16 @@
         <v>136</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12704,10 +12707,10 @@
         <v>78</v>
       </c>
       <c r="S84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="T84" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U84" t="s" s="2">
         <v>78</v>
@@ -12743,7 +12746,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>79</v>
@@ -12761,13 +12764,13 @@
         <v>78</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12775,10 +12778,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12804,13 +12807,13 @@
         <v>103</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12824,7 +12827,7 @@
         <v>78</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>78</v>
@@ -12860,7 +12863,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12878,13 +12881,13 @@
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
@@ -12892,10 +12895,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12918,13 +12921,13 @@
         <v>90</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12975,7 +12978,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12993,13 +12996,13 @@
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -13007,10 +13010,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13033,16 +13036,16 @@
         <v>90</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13092,7 +13095,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -13110,13 +13113,13 @@
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
@@ -13124,13 +13127,13 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>78</v>
@@ -13152,17 +13155,17 @@
         <v>90</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>78</v>
@@ -13211,7 +13214,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -13220,7 +13223,7 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>101</v>
@@ -13229,24 +13232,24 @@
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13358,10 +13361,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13475,10 +13478,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13504,16 +13507,16 @@
         <v>175</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>78</v>
@@ -13538,13 +13541,13 @@
         <v>78</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>78</v>
@@ -13562,7 +13565,7 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>79</v>
@@ -13583,7 +13586,7 @@
         <v>198</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>78</v>
@@ -13594,10 +13597,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13620,19 +13623,19 @@
         <v>90</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>78</v>
@@ -13642,7 +13645,7 @@
         <v>78</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>78</v>
@@ -13660,10 +13663,10 @@
         <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>78</v>
@@ -13681,7 +13684,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13699,10 +13702,10 @@
         <v>78</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>78</v>
@@ -13713,10 +13716,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13742,16 +13745,16 @@
         <v>136</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
@@ -13761,10 +13764,10 @@
         <v>78</v>
       </c>
       <c r="S93" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>78</v>
@@ -13800,7 +13803,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>79</v>
@@ -13818,13 +13821,13 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13832,10 +13835,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13861,13 +13864,13 @@
         <v>103</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13881,7 +13884,7 @@
         <v>78</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>78</v>
@@ -13917,7 +13920,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13935,13 +13938,13 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13949,10 +13952,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13975,13 +13978,13 @@
         <v>90</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14032,7 +14035,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -14050,13 +14053,13 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -14064,10 +14067,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14090,16 +14093,16 @@
         <v>90</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14149,7 +14152,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -14167,13 +14170,13 @@
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14181,13 +14184,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>78</v>
@@ -14209,17 +14212,17 @@
         <v>90</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>78</v>
@@ -14268,7 +14271,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -14277,7 +14280,7 @@
         <v>80</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>101</v>
@@ -14286,24 +14289,24 @@
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14415,10 +14418,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14532,10 +14535,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14561,16 +14564,16 @@
         <v>175</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>78</v>
@@ -14595,13 +14598,13 @@
         <v>78</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>78</v>
@@ -14619,7 +14622,7 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>79</v>
@@ -14640,7 +14643,7 @@
         <v>198</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>78</v>
@@ -14651,10 +14654,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14677,19 +14680,19 @@
         <v>90</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14699,7 +14702,7 @@
         <v>78</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>78</v>
@@ -14717,10 +14720,10 @@
         <v>157</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>78</v>
@@ -14738,7 +14741,7 @@
         <v>78</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>79</v>
@@ -14756,10 +14759,10 @@
         <v>78</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>78</v>
@@ -14770,10 +14773,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14799,16 +14802,16 @@
         <v>136</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
@@ -14818,10 +14821,10 @@
         <v>78</v>
       </c>
       <c r="S102" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>78</v>
@@ -14857,7 +14860,7 @@
         <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>79</v>
@@ -14875,13 +14878,13 @@
         <v>78</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14889,10 +14892,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14918,13 +14921,13 @@
         <v>103</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -14938,7 +14941,7 @@
         <v>78</v>
       </c>
       <c r="T103" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="U103" t="s" s="2">
         <v>78</v>
@@ -14974,7 +14977,7 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>79</v>
@@ -14992,13 +14995,13 @@
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>78</v>
@@ -15006,10 +15009,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15032,13 +15035,13 @@
         <v>90</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15089,7 +15092,7 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>79</v>
@@ -15107,13 +15110,13 @@
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>78</v>
@@ -15121,10 +15124,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15147,16 +15150,16 @@
         <v>90</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -15206,7 +15209,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>79</v>
@@ -15224,13 +15227,13 @@
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
@@ -15238,10 +15241,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15264,70 +15267,70 @@
         <v>90</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="R106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q106" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="R106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>79</v>
@@ -15345,24 +15348,24 @@
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15385,19 +15388,19 @@
         <v>90</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15425,16 +15428,16 @@
         <v>165</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AC107" s="2"/>
       <c r="AD107" t="s" s="2">
@@ -15444,7 +15447,7 @@
         <v>116</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>79</v>
@@ -15462,27 +15465,27 @@
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>78</v>
@@ -15504,19 +15507,19 @@
         <v>90</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>78</v>
@@ -15541,11 +15544,11 @@
         <v>78</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>78</v>
@@ -15563,7 +15566,7 @@
         <v>78</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>79</v>
@@ -15581,24 +15584,24 @@
         <v>78</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15710,10 +15713,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15825,13 +15828,13 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>543</v>
       </c>
-      <c r="B111" t="s" s="2">
-        <v>542</v>
-      </c>
       <c r="C111" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D111" t="s" s="2">
         <v>78</v>
@@ -15853,13 +15856,13 @@
         <v>78</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15942,10 +15945,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16057,10 +16060,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -16149,7 +16152,7 @@
         <v>80</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>118</v>
@@ -16172,10 +16175,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16201,13 +16204,13 @@
         <v>136</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -16215,7 +16218,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>78</v>
@@ -16257,7 +16260,7 @@
         <v>78</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>89</v>
@@ -16289,10 +16292,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16318,10 +16321,10 @@
         <v>175</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16333,7 +16336,7 @@
         <v>78</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>78</v>
@@ -16348,11 +16351,11 @@
         <v>78</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>78</v>
@@ -16370,7 +16373,7 @@
         <v>78</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>79</v>
@@ -16379,7 +16382,7 @@
         <v>89</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>101</v>
@@ -16402,10 +16405,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16431,16 +16434,16 @@
         <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>78</v>
@@ -16489,7 +16492,7 @@
         <v>78</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>79</v>
@@ -16507,10 +16510,10 @@
         <v>78</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>78</v>
@@ -16521,10 +16524,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16636,10 +16639,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16753,10 +16756,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16782,16 +16785,16 @@
         <v>136</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>78</v>
@@ -16840,7 +16843,7 @@
         <v>78</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>79</v>
@@ -16858,10 +16861,10 @@
         <v>78</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>78</v>
@@ -16872,10 +16875,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16901,13 +16904,13 @@
         <v>103</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16957,7 +16960,7 @@
         <v>78</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>79</v>
@@ -16975,10 +16978,10 @@
         <v>78</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>78</v>
@@ -16989,10 +16992,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -17018,14 +17021,14 @@
         <v>175</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>78</v>
@@ -17074,7 +17077,7 @@
         <v>78</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>79</v>
@@ -17092,10 +17095,10 @@
         <v>78</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>78</v>
@@ -17106,10 +17109,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -17135,14 +17138,14 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>78</v>
@@ -17191,7 +17194,7 @@
         <v>78</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>79</v>
@@ -17209,10 +17212,10 @@
         <v>78</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>78</v>
@@ -17223,10 +17226,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17249,19 +17252,19 @@
         <v>90</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>78</v>
@@ -17310,7 +17313,7 @@
         <v>78</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>79</v>
@@ -17328,10 +17331,10 @@
         <v>78</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>78</v>
@@ -17342,10 +17345,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17371,16 +17374,16 @@
         <v>103</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>78</v>
@@ -17429,7 +17432,7 @@
         <v>78</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>79</v>
@@ -17447,10 +17450,10 @@
         <v>78</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM124" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN124" t="s" s="2">
         <v>78</v>
@@ -17461,13 +17464,13 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>78</v>
@@ -17489,19 +17492,19 @@
         <v>90</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>78</v>
@@ -17526,11 +17529,11 @@
         <v>78</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>78</v>
@@ -17548,7 +17551,7 @@
         <v>78</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>79</v>
@@ -17566,24 +17569,24 @@
         <v>78</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17695,10 +17698,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17812,10 +17815,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17841,16 +17844,16 @@
         <v>153</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>78</v>
@@ -17899,7 +17902,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17917,10 +17920,10 @@
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -17931,10 +17934,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18046,10 +18049,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -18163,10 +18166,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18192,16 +18195,16 @@
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>78</v>
@@ -18250,7 +18253,7 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>79</v>
@@ -18268,10 +18271,10 @@
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18282,10 +18285,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18311,13 +18314,13 @@
         <v>103</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18367,7 +18370,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18385,10 +18388,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18399,10 +18402,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18428,14 +18431,14 @@
         <v>175</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18484,7 +18487,7 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
@@ -18502,10 +18505,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18516,10 +18519,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18545,14 +18548,14 @@
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>78</v>
@@ -18601,7 +18604,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18619,10 +18622,10 @@
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18633,10 +18636,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -18659,19 +18662,19 @@
         <v>90</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>78</v>
@@ -18720,7 +18723,7 @@
         <v>78</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
@@ -18738,10 +18741,10 @@
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18752,10 +18755,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18781,16 +18784,16 @@
         <v>103</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18839,7 +18842,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18857,10 +18860,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18871,13 +18874,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>78</v>
@@ -18899,19 +18902,19 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>78</v>
@@ -18936,11 +18939,11 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y137" s="2"/>
       <c r="Z137" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -18958,7 +18961,7 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
@@ -18976,24 +18979,24 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN137" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19105,10 +19108,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -19222,10 +19225,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19251,16 +19254,16 @@
         <v>153</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19309,7 +19312,7 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
@@ -19327,10 +19330,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19341,10 +19344,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19456,10 +19459,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -19573,10 +19576,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19602,16 +19605,16 @@
         <v>136</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>78</v>
@@ -19660,7 +19663,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19678,10 +19681,10 @@
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19692,10 +19695,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -19721,13 +19724,13 @@
         <v>103</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19777,7 +19780,7 @@
         <v>78</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
@@ -19795,10 +19798,10 @@
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19809,10 +19812,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19838,14 +19841,14 @@
         <v>175</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19894,7 +19897,7 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
@@ -19912,10 +19915,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19926,10 +19929,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19955,14 +19958,14 @@
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>78</v>
@@ -20011,7 +20014,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20029,10 +20032,10 @@
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20043,10 +20046,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -20069,19 +20072,19 @@
         <v>90</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>78</v>
@@ -20130,7 +20133,7 @@
         <v>78</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
@@ -20148,10 +20151,10 @@
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20162,10 +20165,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20191,16 +20194,16 @@
         <v>103</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20249,7 +20252,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20267,10 +20270,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20281,13 +20284,13 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="D149" t="s" s="2">
         <v>78</v>
@@ -20309,19 +20312,19 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>78</v>
@@ -20346,11 +20349,11 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20368,7 +20371,7 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
@@ -20383,27 +20386,27 @@
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN149" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20515,10 +20518,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20607,7 +20610,7 @@
         <v>80</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>118</v>
@@ -20630,13 +20633,13 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D152" t="s" s="2">
         <v>78</v>
@@ -20658,13 +20661,13 @@
         <v>78</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -20724,7 +20727,7 @@
         <v>80</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ152" t="s" s="2">
         <v>118</v>
@@ -20747,10 +20750,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20862,10 +20865,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -20954,7 +20957,7 @@
         <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ154" t="s" s="2">
         <v>118</v>
@@ -20977,10 +20980,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -21006,13 +21009,13 @@
         <v>136</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -21020,7 +21023,7 @@
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21062,7 +21065,7 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>89</v>
@@ -21094,10 +21097,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21123,10 +21126,10 @@
         <v>175</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21138,7 +21141,7 @@
         <v>78</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>78</v>
@@ -21153,11 +21156,11 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y156" s="2"/>
       <c r="Z156" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>78</v>
@@ -21175,7 +21178,7 @@
         <v>78</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
@@ -21184,7 +21187,7 @@
         <v>89</v>
       </c>
       <c r="AI156" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ156" t="s" s="2">
         <v>101</v>
@@ -21207,10 +21210,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -21236,16 +21239,16 @@
         <v>153</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P157" t="s" s="2">
         <v>78</v>
@@ -21294,7 +21297,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21303,7 +21306,7 @@
         <v>80</v>
       </c>
       <c r="AI157" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>101</v>
@@ -21312,10 +21315,10 @@
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21326,10 +21329,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21355,16 +21358,16 @@
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>78</v>
@@ -21413,7 +21416,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21422,7 +21425,7 @@
         <v>89</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ158" t="s" s="2">
         <v>101</v>
@@ -21431,10 +21434,10 @@
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21445,13 +21448,13 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D159" t="s" s="2">
         <v>78</v>
@@ -21473,19 +21476,19 @@
         <v>90</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>78</v>
@@ -21510,11 +21513,11 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y159" s="2"/>
       <c r="Z159" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
@@ -21532,7 +21535,7 @@
         <v>78</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21547,27 +21550,27 @@
         <v>101</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21679,10 +21682,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21771,7 +21774,7 @@
         <v>80</v>
       </c>
       <c r="AI161" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ161" t="s" s="2">
         <v>118</v>
@@ -21794,13 +21797,13 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D162" t="s" s="2">
         <v>78</v>
@@ -21822,13 +21825,13 @@
         <v>78</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -21888,7 +21891,7 @@
         <v>80</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>118</v>
@@ -21911,10 +21914,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -22026,10 +22029,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -22118,7 +22121,7 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ164" t="s" s="2">
         <v>118</v>
@@ -22141,10 +22144,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22170,13 +22173,13 @@
         <v>136</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -22184,7 +22187,7 @@
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22226,7 +22229,7 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>89</v>
@@ -22258,10 +22261,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22287,10 +22290,10 @@
         <v>175</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22302,7 +22305,7 @@
         <v>78</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>78</v>
@@ -22317,11 +22320,11 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y166" s="2"/>
       <c r="Z166" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
@@ -22339,7 +22342,7 @@
         <v>78</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
@@ -22348,7 +22351,7 @@
         <v>89</v>
       </c>
       <c r="AI166" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ166" t="s" s="2">
         <v>101</v>
@@ -22371,10 +22374,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -22400,16 +22403,16 @@
         <v>153</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>78</v>
@@ -22458,7 +22461,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22467,7 +22470,7 @@
         <v>80</v>
       </c>
       <c r="AI167" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ167" t="s" s="2">
         <v>101</v>
@@ -22476,10 +22479,10 @@
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22490,10 +22493,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22519,16 +22522,16 @@
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O168" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P168" t="s" s="2">
         <v>78</v>
@@ -22577,7 +22580,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22586,7 +22589,7 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>101</v>
@@ -22595,10 +22598,10 @@
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22609,13 +22612,13 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="D169" t="s" s="2">
         <v>78</v>
@@ -22637,19 +22640,19 @@
         <v>90</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O169" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P169" t="s" s="2">
         <v>78</v>
@@ -22674,11 +22677,11 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y169" s="2"/>
       <c r="Z169" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>78</v>
@@ -22696,7 +22699,7 @@
         <v>78</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22714,24 +22717,24 @@
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN169" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22843,10 +22846,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22935,7 +22938,7 @@
         <v>80</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>118</v>
@@ -22958,13 +22961,13 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D172" t="s" s="2">
         <v>78</v>
@@ -22986,13 +22989,13 @@
         <v>78</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -23052,7 +23055,7 @@
         <v>80</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>118</v>
@@ -23075,10 +23078,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23190,10 +23193,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -23282,7 +23285,7 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ174" t="s" s="2">
         <v>118</v>
@@ -23305,10 +23308,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23334,13 +23337,13 @@
         <v>136</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
@@ -23348,7 +23351,7 @@
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23390,7 +23393,7 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>89</v>
@@ -23422,10 +23425,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23451,10 +23454,10 @@
         <v>175</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23466,7 +23469,7 @@
         <v>78</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>78</v>
@@ -23481,11 +23484,11 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
@@ -23503,7 +23506,7 @@
         <v>78</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
@@ -23512,7 +23515,7 @@
         <v>89</v>
       </c>
       <c r="AI176" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ176" t="s" s="2">
         <v>101</v>
@@ -23535,10 +23538,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -23564,16 +23567,16 @@
         <v>153</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>78</v>
@@ -23622,7 +23625,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23631,7 +23634,7 @@
         <v>80</v>
       </c>
       <c r="AI177" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ177" t="s" s="2">
         <v>101</v>
@@ -23640,10 +23643,10 @@
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23654,10 +23657,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23683,16 +23686,16 @@
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>78</v>
@@ -23741,7 +23744,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23750,7 +23753,7 @@
         <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>101</v>
@@ -23759,10 +23762,10 @@
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23773,13 +23776,13 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D179" t="s" s="2">
         <v>78</v>
@@ -23801,19 +23804,19 @@
         <v>90</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>78</v>
@@ -23841,10 +23844,10 @@
         <v>165</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
@@ -23862,7 +23865,7 @@
         <v>78</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23880,24 +23883,24 @@
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AN179" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -24009,10 +24012,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24101,7 +24104,7 @@
         <v>80</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>118</v>
@@ -24124,13 +24127,13 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D182" t="s" s="2">
         <v>78</v>
@@ -24152,13 +24155,13 @@
         <v>78</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
@@ -24218,7 +24221,7 @@
         <v>80</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>118</v>
@@ -24241,10 +24244,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24356,10 +24359,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -24448,7 +24451,7 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>118</v>
@@ -24471,10 +24474,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24500,13 +24503,13 @@
         <v>136</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
@@ -24514,7 +24517,7 @@
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24556,7 +24559,7 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>89</v>
@@ -24588,10 +24591,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24617,10 +24620,10 @@
         <v>175</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24632,7 +24635,7 @@
         <v>78</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>78</v>
@@ -24647,11 +24650,11 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y186" s="2"/>
       <c r="Z186" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
@@ -24669,7 +24672,7 @@
         <v>78</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
@@ -24678,7 +24681,7 @@
         <v>89</v>
       </c>
       <c r="AI186" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ186" t="s" s="2">
         <v>101</v>
@@ -24701,10 +24704,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -24730,16 +24733,16 @@
         <v>153</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O187" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P187" t="s" s="2">
         <v>78</v>
@@ -24788,7 +24791,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24797,7 +24800,7 @@
         <v>80</v>
       </c>
       <c r="AI187" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ187" t="s" s="2">
         <v>101</v>
@@ -24806,10 +24809,10 @@
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24820,10 +24823,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24849,16 +24852,16 @@
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O188" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P188" t="s" s="2">
         <v>78</v>
@@ -24907,7 +24910,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24916,7 +24919,7 @@
         <v>89</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ188" t="s" s="2">
         <v>101</v>
@@ -24925,10 +24928,10 @@
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -24939,10 +24942,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24968,16 +24971,16 @@
         <v>103</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>78</v>
@@ -25026,7 +25029,7 @@
         <v>78</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
@@ -25035,22 +25038,22 @@
         <v>89</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>78</v>
@@ -25058,10 +25061,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25087,16 +25090,16 @@
         <v>103</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>78</v>
@@ -25145,7 +25148,7 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>79</v>
@@ -25160,13 +25163,13 @@
         <v>101</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>78</v>
@@ -25177,10 +25180,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25203,19 +25206,19 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>78</v>
@@ -25252,7 +25255,7 @@
         <v>78</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AC191" s="2"/>
       <c r="AD191" t="s" s="2">
@@ -25262,7 +25265,7 @@
         <v>116</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
@@ -25274,19 +25277,19 @@
         <v>207</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>78</v>
@@ -25294,10 +25297,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25409,10 +25412,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -25526,13 +25529,13 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="B194" t="s" s="2">
-        <v>689</v>
-      </c>
       <c r="C194" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>78</v>
@@ -25554,13 +25557,13 @@
         <v>78</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -25643,10 +25646,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25672,10 +25675,10 @@
         <v>175</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -25702,13 +25705,13 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>78</v>
@@ -25726,7 +25729,7 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
@@ -25735,7 +25738,7 @@
         <v>89</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>101</v>
@@ -25744,13 +25747,13 @@
         <v>78</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>78</v>
@@ -25758,10 +25761,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25787,16 +25790,16 @@
         <v>103</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>78</v>
@@ -25845,7 +25848,7 @@
         <v>78</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
@@ -25863,13 +25866,13 @@
         <v>78</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25877,10 +25880,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25906,16 +25909,16 @@
         <v>175</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="O197" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="P197" t="s" s="2">
         <v>78</v>
@@ -25940,13 +25943,13 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>78</v>
@@ -25964,7 +25967,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25982,13 +25985,13 @@
         <v>78</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>78</v>
@@ -25996,10 +25999,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -26022,16 +26025,16 @@
         <v>90</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26081,7 +26084,7 @@
         <v>78</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
@@ -26113,10 +26116,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -26139,13 +26142,13 @@
         <v>90</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26196,7 +26199,7 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
@@ -26217,10 +26220,10 @@
         <v>198</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26228,13 +26231,13 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D200" t="s" s="2">
         <v>78</v>
@@ -26256,19 +26259,19 @@
         <v>78</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="P200" t="s" s="2">
         <v>78</v>
@@ -26317,7 +26320,7 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
@@ -26329,19 +26332,19 @@
         <v>207</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>78</v>
@@ -26349,10 +26352,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26375,19 +26378,19 @@
         <v>78</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26436,7 +26439,7 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
@@ -26448,19 +26451,19 @@
         <v>207</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>78</v>
@@ -26468,10 +26471,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26494,17 +26497,17 @@
         <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26553,7 +26556,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26571,10 +26574,10 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AN202" t="s" s="2">
         <v>107</v>
@@ -26585,10 +26588,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26700,10 +26703,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -26817,10 +26820,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -26846,13 +26849,13 @@
         <v>103</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -26902,7 +26905,7 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
@@ -26911,7 +26914,7 @@
         <v>89</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AJ205" t="s" s="2">
         <v>101</v>
@@ -26934,10 +26937,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26963,13 +26966,13 @@
         <v>136</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
@@ -26999,7 +27002,7 @@
       </c>
       <c r="Y206" s="2"/>
       <c r="Z206" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27017,7 +27020,7 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
@@ -27049,10 +27052,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27075,16 +27078,16 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
@@ -27134,7 +27137,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27155,7 +27158,7 @@
         <v>78</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AN207" t="s" s="2">
         <v>78</v>
@@ -27166,10 +27169,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27195,13 +27198,13 @@
         <v>103</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -27251,7 +27254,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27283,10 +27286,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -27309,19 +27312,19 @@
         <v>78</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P209" t="s" s="2">
         <v>78</v>
@@ -27370,7 +27373,7 @@
         <v>78</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27391,7 +27394,7 @@
         <v>78</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>78</v>
@@ -27402,10 +27405,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27517,10 +27520,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -27634,14 +27637,14 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
@@ -27663,16 +27666,16 @@
         <v>110</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N212" t="s" s="2">
         <v>113</v>
       </c>
       <c r="O212" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P212" t="s" s="2">
         <v>78</v>
@@ -27721,7 +27724,7 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
@@ -27753,10 +27756,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27779,17 +27782,17 @@
         <v>78</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N213" s="2"/>
       <c r="O213" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="P213" t="s" s="2">
         <v>78</v>
@@ -27817,10 +27820,10 @@
         <v>157</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -27838,7 +27841,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -27859,7 +27862,7 @@
         <v>78</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>78</v>
@@ -27870,10 +27873,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27896,17 +27899,17 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N214" s="2"/>
       <c r="O214" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -27955,7 +27958,7 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
@@ -27973,10 +27976,10 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AN214" t="s" s="2">
         <v>78</v>
@@ -27987,10 +27990,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28013,17 +28016,17 @@
         <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="P215" t="s" s="2">
         <v>78</v>
@@ -28072,7 +28075,7 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
@@ -28084,19 +28087,19 @@
         <v>207</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28104,10 +28107,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -28130,19 +28133,19 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="P216" t="s" s="2">
         <v>78</v>
@@ -28191,7 +28194,7 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
@@ -28209,13 +28212,13 @@
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28223,10 +28226,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -28249,17 +28252,17 @@
         <v>78</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="N217" s="2"/>
       <c r="O217" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28308,7 +28311,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T08:22:21+00:00</t>
+    <t>2024-07-02T09:45:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T09:45:37+00:00</t>
+    <t>2024-07-02T11:34:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
 per-1</t>
   </si>
   <si>
-    <t>dateCreation</t>
+    <t>EntiteJuridique.dateCreation</t>
   </si>
   <si>
     <t>DR.1</t>
@@ -819,7 +819,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>dateFermeture</t>
+    <t>EntiteJuridique.dateFermeture</t>
   </si>
   <si>
     <t>DR.2</t>
@@ -860,7 +860,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte de la licence d’exploitation d’une officine.</t>
   </si>
   <si>
-    <t>numeroLicenceOfficine</t>
+    <t>EntiteJuridique.numeroLicenceOfficine</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-pricing-model</t>
@@ -895,7 +895,7 @@
     <t>Extension créée dans le cadre de l'Annuaire Santé pour prise en compte du type de fermeture de la structure.</t>
   </si>
   <si>
-    <t>typeFermeture</t>
+    <t>EntiteJuridique.typeFermeture</t>
   </si>
   <si>
     <t>Organization.extension:as-ext-organization-budget-type</t>
@@ -994,7 +994,7 @@
     <t>Identifiant idNat_Struct délivré par une autorité d'enregistrement tel que défini dans l'Annexe Transverse Source des données métier pour les professionnels et les structures.</t>
   </si>
   <si>
-    <t>idNat_struct</t>
+    <t>EntiteJuridique.idNat_struct</t>
   </si>
   <si>
     <t>Organization.identifier:idNatSt.id</t>
@@ -1217,7 +1217,7 @@
     <t>Identifiant SIREN (9 chiffres) ou SIRET (14 chiffres)</t>
   </si>
   <si>
-    <t>numSiren</t>
+    <t>EntiteJuridique.numSiren</t>
   </si>
   <si>
     <t>Organization.identifier:sirene.id</t>
@@ -1470,7 +1470,7 @@
     <t>Identifiant FINESS Entité Géographique (EG) ou Entité Juridique (EJ)</t>
   </si>
   <si>
-    <t>numFiness</t>
+    <t>EntiteJuridique.numFiness</t>
   </si>
   <si>
     <t>Organization.identifier:finess.id</t>
@@ -1918,7 +1918,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J99-InseeNAFrav2Niveau5-RASS/FHIR/JDV-J99-InseeNAFrav2Niveau5-RASS</t>
   </si>
   <si>
-    <t>codeAPEN</t>
+    <t>EntiteJuridique.codeAPEN</t>
   </si>
   <si>
     <t>Organization.type:activiteINSEE.id</t>
@@ -1960,7 +1960,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J100-FinessStatutJuridique-RASS/FHIR/JDV-J100-FinessStatutJuridique-RASS</t>
   </si>
   <si>
-    <t>statutJuridique</t>
+    <t>EntiteJuridique.statutJuridique</t>
   </si>
   <si>
     <t>Organization.type:statutJuridiqueINSEE.id</t>
@@ -2080,7 +2080,7 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
-    <t>raisonSociale</t>
+    <t>EntiteJuridique.raisonSociale</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -2108,7 +2108,7 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>raisonSocialeLongue</t>
+    <t>EntiteJuridique.raisonSocialeLongue</t>
   </si>
   <si>
     <t>Organization.telecom</t>
@@ -2138,7 +2138,7 @@
 ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>telecommunication</t>
+    <t>EntiteJuridique.telecommunication</t>
   </si>
   <si>
     <t>XTN</t>
@@ -2307,7 +2307,7 @@
     <t>Les BALs MSS de type ORG ou APP rattachées à une personne morale responsable de l’accès et de l’usage de la BAL (boiteLettreMSS).</t>
   </si>
   <si>
-    <t>boiteLettreMSS</t>
+    <t>EntiteJuridique.boiteLettreMSS</t>
   </si>
   <si>
     <t>Organization.address</t>
@@ -2333,7 +2333,7 @@
 org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
   </si>
   <si>
-    <t>adresseEJ</t>
+    <t>EntiteJuridique.adresseEJ</t>
   </si>
   <si>
     <t>XAD</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$222</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8077" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8257" uniqueCount="828">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:34:04+00:00</t>
+    <t>2024-07-02T11:51:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1831,6 +1831,21 @@
   </si>
   <si>
     <t>Organization.type:secteurActiviteRASS.extension</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.id</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.extension</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.url</t>
+  </si>
+  <si>
+    <t>Organization.type:secteurActiviteRASS.extension:as-ext-organization-types.value[x]</t>
   </si>
   <si>
     <t>Organization.type:secteurActiviteRASS.coding</t>
@@ -2885,7 +2900,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO217"/>
+  <dimension ref="A1:AO222"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="80.17578125" customWidth="true" bestFit="true"/>
@@ -17705,11 +17720,11 @@
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>80</v>
@@ -17727,14 +17742,12 @@
         <v>110</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>78</v>
@@ -17804,7 +17817,7 @@
         <v>78</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>78</v>
@@ -17818,9 +17831,11 @@
         <v>585</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D128" t="s" s="2">
         <v>78</v>
       </c>
@@ -17838,23 +17853,19 @@
         <v>78</v>
       </c>
       <c r="J128" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O128" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>78</v>
       </c>
@@ -17902,7 +17913,7 @@
         <v>78</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>79</v>
@@ -17914,16 +17925,16 @@
         <v>78</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>78</v>
@@ -17937,7 +17948,7 @@
         <v>586</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -18052,18 +18063,18 @@
         <v>587</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>565</v>
+        <v>552</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>78</v>
@@ -18078,14 +18089,12 @@
         <v>110</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>111</v>
+        <v>200</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>78</v>
@@ -18143,7 +18152,7 @@
         <v>80</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>118</v>
@@ -18155,7 +18164,7 @@
         <v>78</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AN130" t="s" s="2">
         <v>78</v>
@@ -18169,7 +18178,7 @@
         <v>588</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>567</v>
+        <v>554</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -18189,29 +18198,27 @@
         <v>78</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>408</v>
+        <v>223</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>409</v>
+        <v>224</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>78</v>
@@ -18253,10 +18260,10 @@
         <v>78</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>413</v>
+        <v>227</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>89</v>
@@ -18265,16 +18272,16 @@
         <v>78</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK131" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL131" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>415</v>
+        <v>198</v>
       </c>
       <c r="AN131" t="s" s="2">
         <v>78</v>
@@ -18288,7 +18295,7 @@
         <v>589</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18308,20 +18315,18 @@
         <v>78</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>418</v>
+        <v>231</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>78</v>
@@ -18331,7 +18336,7 @@
         <v>78</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>78</v>
+        <v>580</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>78</v>
@@ -18346,13 +18351,11 @@
         <v>78</v>
       </c>
       <c r="X132" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y132" s="2"/>
       <c r="Z132" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>78</v>
@@ -18370,7 +18373,7 @@
         <v>78</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>421</v>
+        <v>233</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>79</v>
@@ -18379,7 +18382,7 @@
         <v>89</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>101</v>
@@ -18388,10 +18391,10 @@
         <v>78</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>423</v>
+        <v>198</v>
       </c>
       <c r="AN132" t="s" s="2">
         <v>78</v>
@@ -18405,7 +18408,7 @@
         <v>590</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18413,7 +18416,7 @@
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G133" t="s" s="2">
         <v>89</v>
@@ -18428,17 +18431,19 @@
         <v>90</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>572</v>
+        <v>395</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O133" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>78</v>
@@ -18487,13 +18492,13 @@
         <v>78</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>78</v>
@@ -18505,10 +18510,10 @@
         <v>78</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="AN133" t="s" s="2">
         <v>78</v>
@@ -18522,7 +18527,7 @@
         <v>591</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -18542,21 +18547,19 @@
         <v>78</v>
       </c>
       <c r="J134" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K134" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>435</v>
+        <v>105</v>
       </c>
       <c r="N134" s="2"/>
-      <c r="O134" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
         <v>78</v>
       </c>
@@ -18604,7 +18607,7 @@
         <v>78</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>437</v>
+        <v>106</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>79</v>
@@ -18616,16 +18619,16 @@
         <v>78</v>
       </c>
       <c r="AJ134" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK134" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>439</v>
+        <v>107</v>
       </c>
       <c r="AN134" t="s" s="2">
         <v>78</v>
@@ -18639,18 +18642,18 @@
         <v>592</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>78</v>
@@ -18659,23 +18662,21 @@
         <v>78</v>
       </c>
       <c r="J135" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>443</v>
+        <v>111</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>444</v>
+        <v>112</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>78</v>
       </c>
@@ -18711,40 +18712,40 @@
         <v>78</v>
       </c>
       <c r="AB135" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC135" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE135" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>447</v>
+        <v>117</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK135" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL135" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>449</v>
+        <v>107</v>
       </c>
       <c r="AN135" t="s" s="2">
         <v>78</v>
@@ -18758,7 +18759,7 @@
         <v>593</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -18766,7 +18767,7 @@
       </c>
       <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>89</v>
@@ -18781,19 +18782,19 @@
         <v>90</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>78</v>
@@ -18842,7 +18843,7 @@
         <v>78</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>79</v>
@@ -18860,10 +18861,10 @@
         <v>78</v>
       </c>
       <c r="AL136" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AM136" t="s" s="2">
-        <v>458</v>
+        <v>415</v>
       </c>
       <c r="AN136" t="s" s="2">
         <v>78</v>
@@ -18877,11 +18878,9 @@
         <v>594</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C137" t="s" s="2">
-        <v>595</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>78</v>
       </c>
@@ -18902,20 +18901,18 @@
         <v>90</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>596</v>
+        <v>418</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>527</v>
+        <v>419</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O137" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>78</v>
       </c>
@@ -18939,11 +18936,13 @@
         <v>78</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y137" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y137" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z137" t="s" s="2">
-        <v>597</v>
+        <v>78</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>78</v>
@@ -18961,13 +18960,13 @@
         <v>78</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>525</v>
+        <v>421</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>78</v>
@@ -18979,24 +18978,24 @@
         <v>78</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>533</v>
+        <v>422</v>
       </c>
       <c r="AM137" t="s" s="2">
-        <v>534</v>
+        <v>423</v>
       </c>
       <c r="AN137" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO137" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -19016,19 +19015,21 @@
         <v>78</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>104</v>
+        <v>572</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>105</v>
+        <v>427</v>
       </c>
       <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>78</v>
       </c>
@@ -19076,7 +19077,7 @@
         <v>78</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>106</v>
+        <v>429</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>79</v>
@@ -19088,16 +19089,16 @@
         <v>78</v>
       </c>
       <c r="AJ138" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK138" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>78</v>
+        <v>430</v>
       </c>
       <c r="AM138" t="s" s="2">
-        <v>107</v>
+        <v>431</v>
       </c>
       <c r="AN138" t="s" s="2">
         <v>78</v>
@@ -19108,21 +19109,21 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H139" t="s" s="2">
         <v>78</v>
@@ -19131,21 +19132,21 @@
         <v>78</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>111</v>
+        <v>434</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N139" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O139" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>78</v>
       </c>
@@ -19181,40 +19182,40 @@
         <v>78</v>
       </c>
       <c r="AB139" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC139" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE139" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>117</v>
+        <v>437</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK139" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL139" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AM139" t="s" s="2">
-        <v>107</v>
+        <v>439</v>
       </c>
       <c r="AN139" t="s" s="2">
         <v>78</v>
@@ -19225,10 +19226,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -19236,7 +19237,7 @@
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s" s="2">
         <v>89</v>
@@ -19251,19 +19252,19 @@
         <v>90</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>153</v>
+        <v>442</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>395</v>
+        <v>443</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>396</v>
+        <v>444</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>397</v>
+        <v>445</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>398</v>
+        <v>446</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>78</v>
@@ -19312,13 +19313,13 @@
         <v>78</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>399</v>
+        <v>447</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>78</v>
@@ -19330,10 +19331,10 @@
         <v>78</v>
       </c>
       <c r="AL140" t="s" s="2">
-        <v>400</v>
+        <v>448</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>401</v>
+        <v>449</v>
       </c>
       <c r="AN140" t="s" s="2">
         <v>78</v>
@@ -19344,10 +19345,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -19367,19 +19368,23 @@
         <v>78</v>
       </c>
       <c r="J141" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K141" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O141" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P141" t="s" s="2">
         <v>78</v>
       </c>
@@ -19427,7 +19432,7 @@
         <v>78</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>79</v>
@@ -19439,16 +19444,16 @@
         <v>78</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK141" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL141" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN141" t="s" s="2">
         <v>78</v>
@@ -19459,21 +19464,23 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C142" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="D142" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>78</v>
@@ -19482,21 +19489,23 @@
         <v>78</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>111</v>
+        <v>601</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>112</v>
+        <v>527</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O142" s="2"/>
+        <v>528</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P142" t="s" s="2">
         <v>78</v>
       </c>
@@ -19520,31 +19529,29 @@
         <v>78</v>
       </c>
       <c r="X142" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y142" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y142" s="2"/>
       <c r="Z142" t="s" s="2">
-        <v>78</v>
+        <v>602</v>
       </c>
       <c r="AA142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>79</v>
@@ -19556,22 +19563,22 @@
         <v>78</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL142" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM142" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AN142" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AN142" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="AO142" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="143" hidden="true">
@@ -19579,7 +19586,7 @@
         <v>603</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>567</v>
+        <v>541</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -19587,7 +19594,7 @@
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G143" t="s" s="2">
         <v>89</v>
@@ -19599,23 +19606,19 @@
         <v>78</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>408</v>
+        <v>104</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>78</v>
       </c>
@@ -19663,7 +19666,7 @@
         <v>78</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>79</v>
@@ -19675,16 +19678,16 @@
         <v>78</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL143" t="s" s="2">
-        <v>414</v>
+        <v>78</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>415</v>
+        <v>107</v>
       </c>
       <c r="AN143" t="s" s="2">
         <v>78</v>
@@ -19698,18 +19701,18 @@
         <v>604</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>78</v>
@@ -19718,19 +19721,19 @@
         <v>78</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>418</v>
+        <v>111</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>419</v>
+        <v>112</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>420</v>
+        <v>113</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -19768,40 +19771,40 @@
         <v>78</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC144" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>421</v>
+        <v>117</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ144" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK144" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL144" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AM144" t="s" s="2">
-        <v>423</v>
+        <v>107</v>
       </c>
       <c r="AN144" t="s" s="2">
         <v>78</v>
@@ -19815,7 +19818,7 @@
         <v>605</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>571</v>
+        <v>561</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -19823,7 +19826,7 @@
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G145" t="s" s="2">
         <v>89</v>
@@ -19838,17 +19841,19 @@
         <v>90</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>175</v>
+        <v>153</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>572</v>
+        <v>395</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N145" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O145" t="s" s="2">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>78</v>
@@ -19897,13 +19902,13 @@
         <v>78</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>78</v>
@@ -19915,10 +19920,10 @@
         <v>78</v>
       </c>
       <c r="AL145" t="s" s="2">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AM145" t="s" s="2">
-        <v>431</v>
+        <v>401</v>
       </c>
       <c r="AN145" t="s" s="2">
         <v>78</v>
@@ -19932,7 +19937,7 @@
         <v>606</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>574</v>
+        <v>563</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -19952,21 +19957,19 @@
         <v>78</v>
       </c>
       <c r="J146" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K146" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>434</v>
+        <v>104</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>435</v>
+        <v>105</v>
       </c>
       <c r="N146" s="2"/>
-      <c r="O146" t="s" s="2">
-        <v>436</v>
-      </c>
+      <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
         <v>78</v>
       </c>
@@ -20014,7 +20017,7 @@
         <v>78</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>437</v>
+        <v>106</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>79</v>
@@ -20026,16 +20029,16 @@
         <v>78</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK146" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL146" t="s" s="2">
-        <v>438</v>
+        <v>78</v>
       </c>
       <c r="AM146" t="s" s="2">
-        <v>439</v>
+        <v>107</v>
       </c>
       <c r="AN146" t="s" s="2">
         <v>78</v>
@@ -20049,18 +20052,18 @@
         <v>607</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>78</v>
@@ -20069,23 +20072,21 @@
         <v>78</v>
       </c>
       <c r="J147" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>442</v>
+        <v>110</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>443</v>
+        <v>111</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>444</v>
+        <v>112</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="O147" t="s" s="2">
-        <v>446</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>78</v>
       </c>
@@ -20121,40 +20122,40 @@
         <v>78</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>447</v>
+        <v>117</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL147" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>449</v>
+        <v>107</v>
       </c>
       <c r="AN147" t="s" s="2">
         <v>78</v>
@@ -20168,7 +20169,7 @@
         <v>608</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -20176,7 +20177,7 @@
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G148" t="s" s="2">
         <v>89</v>
@@ -20191,19 +20192,19 @@
         <v>90</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>452</v>
+        <v>408</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>453</v>
+        <v>409</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>454</v>
+        <v>410</v>
       </c>
       <c r="O148" t="s" s="2">
-        <v>455</v>
+        <v>411</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>78</v>
@@ -20252,7 +20253,7 @@
         <v>78</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>456</v>
+        <v>413</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>79</v>
@@ -20270,10 +20271,10 @@
         <v>78</v>
       </c>
       <c r="AL148" t="s" s="2">
-        <v>457</v>
+        <v>414</v>
       </c>
       <c r="AM148" t="s" s="2">
-        <v>458</v>
+        <v>415</v>
       </c>
       <c r="AN148" t="s" s="2">
         <v>78</v>
@@ -20287,11 +20288,9 @@
         <v>609</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C149" t="s" s="2">
-        <v>610</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>78</v>
       </c>
@@ -20312,20 +20311,18 @@
         <v>90</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>611</v>
+        <v>418</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>527</v>
+        <v>419</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="O149" s="2"/>
       <c r="P149" t="s" s="2">
         <v>78</v>
       </c>
@@ -20349,11 +20346,13 @@
         <v>78</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y149" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z149" t="s" s="2">
-        <v>612</v>
+        <v>78</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>78</v>
@@ -20371,13 +20370,13 @@
         <v>78</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>525</v>
+        <v>421</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>78</v>
@@ -20386,27 +20385,27 @@
         <v>101</v>
       </c>
       <c r="AK149" t="s" s="2">
-        <v>613</v>
+        <v>78</v>
       </c>
       <c r="AL149" t="s" s="2">
-        <v>533</v>
+        <v>422</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>534</v>
+        <v>423</v>
       </c>
       <c r="AN149" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO149" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -20426,19 +20425,21 @@
         <v>78</v>
       </c>
       <c r="J150" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>104</v>
+        <v>572</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>105</v>
+        <v>427</v>
       </c>
       <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+      <c r="O150" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P150" t="s" s="2">
         <v>78</v>
       </c>
@@ -20486,7 +20487,7 @@
         <v>78</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>106</v>
+        <v>429</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>79</v>
@@ -20498,16 +20499,16 @@
         <v>78</v>
       </c>
       <c r="AJ150" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK150" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL150" t="s" s="2">
-        <v>78</v>
+        <v>430</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>107</v>
+        <v>431</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>78</v>
@@ -20518,10 +20519,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>543</v>
+        <v>574</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -20529,10 +20530,10 @@
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H151" t="s" s="2">
         <v>78</v>
@@ -20541,19 +20542,21 @@
         <v>78</v>
       </c>
       <c r="J151" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>200</v>
+        <v>434</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>201</v>
+        <v>435</v>
       </c>
       <c r="N151" s="2"/>
-      <c r="O151" s="2"/>
+      <c r="O151" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P151" t="s" s="2">
         <v>78</v>
       </c>
@@ -20589,40 +20592,40 @@
         <v>78</v>
       </c>
       <c r="AB151" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC151" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE151" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>117</v>
+        <v>437</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH151" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ151" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK151" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL151" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AM151" t="s" s="2">
-        <v>78</v>
+        <v>439</v>
       </c>
       <c r="AN151" t="s" s="2">
         <v>78</v>
@@ -20633,20 +20636,18 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C152" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>576</v>
+      </c>
+      <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G152" t="s" s="2">
         <v>89</v>
@@ -20658,19 +20659,23 @@
         <v>78</v>
       </c>
       <c r="J152" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>546</v>
+        <v>442</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>547</v>
+        <v>443</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N152" s="2"/>
-      <c r="O152" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N152" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="O152" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="P152" t="s" s="2">
         <v>78</v>
       </c>
@@ -20718,28 +20723,28 @@
         <v>78</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>117</v>
+        <v>447</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI152" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK152" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL152" t="s" s="2">
-        <v>78</v>
+        <v>448</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>78</v>
+        <v>449</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>78</v>
@@ -20750,10 +20755,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -20773,19 +20778,23 @@
         <v>78</v>
       </c>
       <c r="J153" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K153" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N153" s="2"/>
-      <c r="O153" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N153" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O153" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P153" t="s" s="2">
         <v>78</v>
       </c>
@@ -20833,7 +20842,7 @@
         <v>78</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>79</v>
@@ -20845,16 +20854,16 @@
         <v>78</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL153" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM153" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN153" t="s" s="2">
         <v>78</v>
@@ -20865,12 +20874,14 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C154" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C154" t="s" s="2">
+        <v>615</v>
+      </c>
       <c r="D154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20879,7 +20890,7 @@
         <v>79</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>78</v>
@@ -20888,19 +20899,23 @@
         <v>78</v>
       </c>
       <c r="J154" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>200</v>
+        <v>616</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O154" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P154" t="s" s="2">
         <v>78</v>
       </c>
@@ -20924,31 +20939,29 @@
         <v>78</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y154" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y154" s="2"/>
       <c r="Z154" t="s" s="2">
-        <v>78</v>
+        <v>617</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>79</v>
@@ -20957,25 +20970,25 @@
         <v>80</v>
       </c>
       <c r="AI154" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK154" t="s" s="2">
-        <v>78</v>
+        <v>618</v>
       </c>
       <c r="AL154" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM154" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN154" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO154" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="155" hidden="true">
@@ -20983,7 +20996,7 @@
         <v>619</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -20991,7 +21004,7 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>89</v>
@@ -21006,24 +21019,22 @@
         <v>78</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N155" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q155" s="2"/>
       <c r="R155" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S155" t="s" s="2">
         <v>78</v>
@@ -21065,10 +21076,10 @@
         <v>78</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>89</v>
@@ -21086,7 +21097,7 @@
         <v>78</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>78</v>
@@ -21100,7 +21111,7 @@
         <v>620</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -21108,10 +21119,10 @@
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H156" t="s" s="2">
         <v>78</v>
@@ -21123,13 +21134,13 @@
         <v>78</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -21141,7 +21152,7 @@
         <v>78</v>
       </c>
       <c r="S156" t="s" s="2">
-        <v>610</v>
+        <v>78</v>
       </c>
       <c r="T156" t="s" s="2">
         <v>78</v>
@@ -21156,41 +21167,43 @@
         <v>78</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y156" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z156" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB156" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC156" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD156" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE156" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH156" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI156" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK156" t="s" s="2">
         <v>78</v>
@@ -21199,7 +21212,7 @@
         <v>78</v>
       </c>
       <c r="AM156" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN156" t="s" s="2">
         <v>78</v>
@@ -21213,18 +21226,20 @@
         <v>621</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C157" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C157" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>78</v>
@@ -21233,23 +21248,19 @@
         <v>78</v>
       </c>
       <c r="J157" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
         <v>78</v>
       </c>
@@ -21297,7 +21308,7 @@
         <v>78</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>79</v>
@@ -21309,16 +21320,16 @@
         <v>207</v>
       </c>
       <c r="AJ157" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK157" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL157" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM157" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN157" t="s" s="2">
         <v>78</v>
@@ -21332,7 +21343,7 @@
         <v>622</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -21352,23 +21363,19 @@
         <v>78</v>
       </c>
       <c r="J158" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K158" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
         <v>78</v>
       </c>
@@ -21416,7 +21423,7 @@
         <v>78</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>79</v>
@@ -21425,19 +21432,19 @@
         <v>89</v>
       </c>
       <c r="AI158" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL158" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM158" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN158" t="s" s="2">
         <v>78</v>
@@ -21451,11 +21458,9 @@
         <v>623</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C159" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21464,7 +21469,7 @@
         <v>79</v>
       </c>
       <c r="G159" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H159" t="s" s="2">
         <v>78</v>
@@ -21473,23 +21478,19 @@
         <v>78</v>
       </c>
       <c r="J159" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>625</v>
+        <v>200</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O159" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
         <v>78</v>
       </c>
@@ -21513,29 +21514,31 @@
         <v>78</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y159" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z159" t="s" s="2">
-        <v>626</v>
+        <v>78</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB159" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC159" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD159" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE159" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>79</v>
@@ -21544,33 +21547,33 @@
         <v>80</v>
       </c>
       <c r="AI159" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ159" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>627</v>
+        <v>78</v>
       </c>
       <c r="AL159" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -21578,7 +21581,7 @@
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G160" t="s" s="2">
         <v>89</v>
@@ -21593,22 +21596,24 @@
         <v>78</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N160" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N160" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q160" s="2"/>
       <c r="R160" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S160" t="s" s="2">
         <v>78</v>
@@ -21650,10 +21655,10 @@
         <v>78</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>89</v>
@@ -21671,7 +21676,7 @@
         <v>78</v>
       </c>
       <c r="AM160" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN160" t="s" s="2">
         <v>78</v>
@@ -21682,10 +21687,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -21693,10 +21698,10 @@
       </c>
       <c r="E161" s="2"/>
       <c r="F161" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>78</v>
@@ -21708,13 +21713,13 @@
         <v>78</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>201</v>
+        <v>558</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
@@ -21726,7 +21731,7 @@
         <v>78</v>
       </c>
       <c r="S161" t="s" s="2">
-        <v>78</v>
+        <v>615</v>
       </c>
       <c r="T161" t="s" s="2">
         <v>78</v>
@@ -21741,43 +21746,41 @@
         <v>78</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB161" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC161" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD161" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE161" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK161" t="s" s="2">
         <v>78</v>
@@ -21786,7 +21789,7 @@
         <v>78</v>
       </c>
       <c r="AM161" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN161" t="s" s="2">
         <v>78</v>
@@ -21797,23 +21800,21 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C162" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E162" s="2"/>
       <c r="F162" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>78</v>
@@ -21822,19 +21823,23 @@
         <v>78</v>
       </c>
       <c r="J162" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>546</v>
+        <v>153</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N162" s="2"/>
-      <c r="O162" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N162" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P162" t="s" s="2">
         <v>78</v>
       </c>
@@ -21882,7 +21887,7 @@
         <v>78</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>79</v>
@@ -21894,16 +21899,16 @@
         <v>207</v>
       </c>
       <c r="AJ162" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK162" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL162" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM162" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN162" t="s" s="2">
         <v>78</v>
@@ -21914,10 +21919,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -21937,19 +21942,23 @@
         <v>78</v>
       </c>
       <c r="J163" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K163" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N163" s="2"/>
-      <c r="O163" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N163" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O163" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P163" t="s" s="2">
         <v>78</v>
       </c>
@@ -21997,7 +22006,7 @@
         <v>78</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>79</v>
@@ -22006,19 +22015,19 @@
         <v>89</v>
       </c>
       <c r="AI163" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL163" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM163" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN163" t="s" s="2">
         <v>78</v>
@@ -22029,12 +22038,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C164" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C164" t="s" s="2">
+        <v>629</v>
+      </c>
       <c r="D164" t="s" s="2">
         <v>78</v>
       </c>
@@ -22043,7 +22054,7 @@
         <v>79</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>78</v>
@@ -22052,19 +22063,23 @@
         <v>78</v>
       </c>
       <c r="J164" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>200</v>
+        <v>630</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N164" s="2"/>
-      <c r="O164" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N164" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P164" t="s" s="2">
         <v>78</v>
       </c>
@@ -22088,31 +22103,29 @@
         <v>78</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>78</v>
+        <v>631</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB164" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC164" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD164" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE164" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>79</v>
@@ -22121,25 +22134,25 @@
         <v>80</v>
       </c>
       <c r="AI164" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ164" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>78</v>
+        <v>632</v>
       </c>
       <c r="AL164" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="165" hidden="true">
@@ -22147,7 +22160,7 @@
         <v>633</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -22155,7 +22168,7 @@
       </c>
       <c r="E165" s="2"/>
       <c r="F165" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G165" t="s" s="2">
         <v>89</v>
@@ -22170,24 +22183,22 @@
         <v>78</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N165" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N165" s="2"/>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q165" s="2"/>
       <c r="R165" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S165" t="s" s="2">
         <v>78</v>
@@ -22229,10 +22240,10 @@
         <v>78</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>89</v>
@@ -22250,7 +22261,7 @@
         <v>78</v>
       </c>
       <c r="AM165" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN165" t="s" s="2">
         <v>78</v>
@@ -22264,7 +22275,7 @@
         <v>634</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -22272,10 +22283,10 @@
       </c>
       <c r="E166" s="2"/>
       <c r="F166" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H166" t="s" s="2">
         <v>78</v>
@@ -22287,13 +22298,13 @@
         <v>78</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -22305,7 +22316,7 @@
         <v>78</v>
       </c>
       <c r="S166" t="s" s="2">
-        <v>624</v>
+        <v>78</v>
       </c>
       <c r="T166" t="s" s="2">
         <v>78</v>
@@ -22320,41 +22331,43 @@
         <v>78</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y166" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z166" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC166" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD166" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH166" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI166" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ166" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK166" t="s" s="2">
         <v>78</v>
@@ -22363,7 +22376,7 @@
         <v>78</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>78</v>
@@ -22377,18 +22390,20 @@
         <v>635</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C167" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C167" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E167" s="2"/>
       <c r="F167" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G167" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H167" t="s" s="2">
         <v>78</v>
@@ -22397,23 +22412,19 @@
         <v>78</v>
       </c>
       <c r="J167" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N167" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N167" s="2"/>
+      <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
         <v>78</v>
       </c>
@@ -22461,7 +22472,7 @@
         <v>78</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>79</v>
@@ -22473,16 +22484,16 @@
         <v>207</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL167" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>78</v>
@@ -22496,7 +22507,7 @@
         <v>636</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -22516,23 +22527,19 @@
         <v>78</v>
       </c>
       <c r="J168" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K168" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N168" s="2"/>
+      <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
         <v>78</v>
       </c>
@@ -22580,7 +22587,7 @@
         <v>78</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>79</v>
@@ -22589,19 +22596,19 @@
         <v>89</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ168" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK168" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>78</v>
@@ -22615,11 +22622,9 @@
         <v>637</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>638</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>78</v>
       </c>
@@ -22628,7 +22633,7 @@
         <v>79</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>78</v>
@@ -22637,23 +22642,19 @@
         <v>78</v>
       </c>
       <c r="J169" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>639</v>
+        <v>200</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O169" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N169" s="2"/>
+      <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
         <v>78</v>
       </c>
@@ -22677,29 +22678,31 @@
         <v>78</v>
       </c>
       <c r="X169" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y169" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y169" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z169" t="s" s="2">
-        <v>640</v>
+        <v>78</v>
       </c>
       <c r="AA169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB169" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE169" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>79</v>
@@ -22708,33 +22711,33 @@
         <v>80</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ169" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK169" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL169" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AN169" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO169" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -22742,7 +22745,7 @@
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>89</v>
@@ -22757,22 +22760,24 @@
         <v>78</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N170" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N170" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S170" t="s" s="2">
         <v>78</v>
@@ -22814,10 +22819,10 @@
         <v>78</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>89</v>
@@ -22835,7 +22840,7 @@
         <v>78</v>
       </c>
       <c r="AM170" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN170" t="s" s="2">
         <v>78</v>
@@ -22846,10 +22851,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -22857,10 +22862,10 @@
       </c>
       <c r="E171" s="2"/>
       <c r="F171" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>78</v>
@@ -22872,13 +22877,13 @@
         <v>78</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>201</v>
+        <v>558</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -22890,7 +22895,7 @@
         <v>78</v>
       </c>
       <c r="S171" t="s" s="2">
-        <v>78</v>
+        <v>629</v>
       </c>
       <c r="T171" t="s" s="2">
         <v>78</v>
@@ -22905,43 +22910,41 @@
         <v>78</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB171" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC171" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD171" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE171" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK171" t="s" s="2">
         <v>78</v>
@@ -22950,7 +22953,7 @@
         <v>78</v>
       </c>
       <c r="AM171" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN171" t="s" s="2">
         <v>78</v>
@@ -22961,23 +22964,21 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C172" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E172" s="2"/>
       <c r="F172" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>78</v>
@@ -22986,19 +22987,23 @@
         <v>78</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>546</v>
+        <v>153</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N172" s="2"/>
-      <c r="O172" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N172" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O172" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P172" t="s" s="2">
         <v>78</v>
       </c>
@@ -23046,7 +23051,7 @@
         <v>78</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>79</v>
@@ -23058,16 +23063,16 @@
         <v>207</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL172" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM172" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN172" t="s" s="2">
         <v>78</v>
@@ -23078,10 +23083,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -23101,19 +23106,23 @@
         <v>78</v>
       </c>
       <c r="J173" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K173" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N173" s="2"/>
-      <c r="O173" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N173" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O173" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P173" t="s" s="2">
         <v>78</v>
       </c>
@@ -23161,7 +23170,7 @@
         <v>78</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>79</v>
@@ -23170,19 +23179,19 @@
         <v>89</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL173" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM173" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN173" t="s" s="2">
         <v>78</v>
@@ -23193,12 +23202,14 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C174" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C174" t="s" s="2">
+        <v>643</v>
+      </c>
       <c r="D174" t="s" s="2">
         <v>78</v>
       </c>
@@ -23207,7 +23218,7 @@
         <v>79</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>78</v>
@@ -23216,19 +23227,23 @@
         <v>78</v>
       </c>
       <c r="J174" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>200</v>
+        <v>644</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N174" s="2"/>
-      <c r="O174" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N174" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P174" t="s" s="2">
         <v>78</v>
       </c>
@@ -23252,31 +23267,29 @@
         <v>78</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>78</v>
+        <v>645</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB174" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC174" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE174" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>79</v>
@@ -23285,25 +23298,25 @@
         <v>80</v>
       </c>
       <c r="AI174" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ174" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK174" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL174" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM174" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO174" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="175" hidden="true">
@@ -23311,7 +23324,7 @@
         <v>646</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -23319,7 +23332,7 @@
       </c>
       <c r="E175" s="2"/>
       <c r="F175" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G175" t="s" s="2">
         <v>89</v>
@@ -23334,24 +23347,22 @@
         <v>78</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N175" s="2"/>
       <c r="O175" s="2"/>
       <c r="P175" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q175" s="2"/>
       <c r="R175" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S175" t="s" s="2">
         <v>78</v>
@@ -23393,10 +23404,10 @@
         <v>78</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>89</v>
@@ -23414,7 +23425,7 @@
         <v>78</v>
       </c>
       <c r="AM175" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN175" t="s" s="2">
         <v>78</v>
@@ -23428,7 +23439,7 @@
         <v>647</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -23436,10 +23447,10 @@
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G176" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H176" t="s" s="2">
         <v>78</v>
@@ -23451,13 +23462,13 @@
         <v>78</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -23469,7 +23480,7 @@
         <v>78</v>
       </c>
       <c r="S176" t="s" s="2">
-        <v>638</v>
+        <v>78</v>
       </c>
       <c r="T176" t="s" s="2">
         <v>78</v>
@@ -23484,41 +23495,43 @@
         <v>78</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y176" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z176" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB176" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC176" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD176" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE176" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH176" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI176" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>78</v>
@@ -23527,7 +23540,7 @@
         <v>78</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN176" t="s" s="2">
         <v>78</v>
@@ -23541,18 +23554,20 @@
         <v>648</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C177" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C177" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E177" s="2"/>
       <c r="F177" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G177" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H177" t="s" s="2">
         <v>78</v>
@@ -23561,23 +23576,19 @@
         <v>78</v>
       </c>
       <c r="J177" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N177" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N177" s="2"/>
+      <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
         <v>78</v>
       </c>
@@ -23625,7 +23636,7 @@
         <v>78</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>79</v>
@@ -23637,16 +23648,16 @@
         <v>207</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK177" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL177" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM177" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN177" t="s" s="2">
         <v>78</v>
@@ -23660,7 +23671,7 @@
         <v>649</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -23680,23 +23691,19 @@
         <v>78</v>
       </c>
       <c r="J178" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K178" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N178" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O178" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N178" s="2"/>
+      <c r="O178" s="2"/>
       <c r="P178" t="s" s="2">
         <v>78</v>
       </c>
@@ -23744,7 +23751,7 @@
         <v>78</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>79</v>
@@ -23753,19 +23760,19 @@
         <v>89</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ178" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK178" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM178" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN178" t="s" s="2">
         <v>78</v>
@@ -23779,11 +23786,9 @@
         <v>650</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C179" t="s" s="2">
-        <v>651</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23792,7 +23797,7 @@
         <v>79</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>78</v>
@@ -23801,23 +23806,19 @@
         <v>78</v>
       </c>
       <c r="J179" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>331</v>
+        <v>110</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>652</v>
+        <v>200</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="N179" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>529</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N179" s="2"/>
+      <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
         <v>78</v>
       </c>
@@ -23841,31 +23842,31 @@
         <v>78</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>165</v>
+        <v>78</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>530</v>
+        <v>78</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>531</v>
+        <v>78</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB179" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC179" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE179" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>525</v>
+        <v>117</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>79</v>
@@ -23874,33 +23875,33 @@
         <v>80</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ179" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK179" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL179" t="s" s="2">
-        <v>533</v>
+        <v>78</v>
       </c>
       <c r="AM179" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AN179" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AO179" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -23908,7 +23909,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>89</v>
@@ -23923,22 +23924,24 @@
         <v>78</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>104</v>
+        <v>223</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N180" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N180" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q180" s="2"/>
       <c r="R180" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S180" t="s" s="2">
         <v>78</v>
@@ -23980,10 +23983,10 @@
         <v>78</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>106</v>
+        <v>227</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>89</v>
@@ -24001,7 +24004,7 @@
         <v>78</v>
       </c>
       <c r="AM180" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN180" t="s" s="2">
         <v>78</v>
@@ -24012,10 +24015,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -24023,10 +24026,10 @@
       </c>
       <c r="E181" s="2"/>
       <c r="F181" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>78</v>
@@ -24038,13 +24041,13 @@
         <v>78</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>110</v>
+        <v>175</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>200</v>
+        <v>231</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>201</v>
+        <v>558</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -24056,7 +24059,7 @@
         <v>78</v>
       </c>
       <c r="S181" t="s" s="2">
-        <v>78</v>
+        <v>643</v>
       </c>
       <c r="T181" t="s" s="2">
         <v>78</v>
@@ -24071,43 +24074,41 @@
         <v>78</v>
       </c>
       <c r="X181" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y181" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y181" s="2"/>
       <c r="Z181" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB181" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC181" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD181" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE181" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>117</v>
+        <v>233</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH181" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI181" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ181" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK181" t="s" s="2">
         <v>78</v>
@@ -24116,7 +24117,7 @@
         <v>78</v>
       </c>
       <c r="AM181" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AN181" t="s" s="2">
         <v>78</v>
@@ -24127,23 +24128,21 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="C182" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>561</v>
+      </c>
+      <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E182" s="2"/>
       <c r="F182" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G182" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H182" t="s" s="2">
         <v>78</v>
@@ -24152,19 +24151,23 @@
         <v>78</v>
       </c>
       <c r="J182" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>546</v>
+        <v>153</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>547</v>
+        <v>395</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N182" s="2"/>
-      <c r="O182" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P182" t="s" s="2">
         <v>78</v>
       </c>
@@ -24212,7 +24215,7 @@
         <v>78</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>117</v>
+        <v>399</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>79</v>
@@ -24224,16 +24227,16 @@
         <v>207</v>
       </c>
       <c r="AJ182" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK182" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL182" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM182" t="s" s="2">
-        <v>78</v>
+        <v>401</v>
       </c>
       <c r="AN182" t="s" s="2">
         <v>78</v>
@@ -24244,10 +24247,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -24267,19 +24270,23 @@
         <v>78</v>
       </c>
       <c r="J183" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K183" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>104</v>
+        <v>452</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N183" s="2"/>
-      <c r="O183" s="2"/>
+        <v>453</v>
+      </c>
+      <c r="N183" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="O183" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P183" t="s" s="2">
         <v>78</v>
       </c>
@@ -24327,7 +24334,7 @@
         <v>78</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>106</v>
+        <v>456</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>79</v>
@@ -24336,19 +24343,19 @@
         <v>89</v>
       </c>
       <c r="AI183" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ183" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK183" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL183" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN183" t="s" s="2">
         <v>78</v>
@@ -24359,12 +24366,14 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="C184" s="2"/>
+        <v>525</v>
+      </c>
+      <c r="C184" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="D184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24373,7 +24382,7 @@
         <v>79</v>
       </c>
       <c r="G184" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H184" t="s" s="2">
         <v>78</v>
@@ -24382,19 +24391,23 @@
         <v>78</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>110</v>
+        <v>331</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>200</v>
+        <v>657</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N184" s="2"/>
-      <c r="O184" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O184" t="s" s="2">
+        <v>529</v>
+      </c>
       <c r="P184" t="s" s="2">
         <v>78</v>
       </c>
@@ -24418,31 +24431,31 @@
         <v>78</v>
       </c>
       <c r="X184" t="s" s="2">
-        <v>78</v>
+        <v>165</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>78</v>
+        <v>530</v>
       </c>
       <c r="Z184" t="s" s="2">
-        <v>78</v>
+        <v>531</v>
       </c>
       <c r="AA184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB184" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC184" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE184" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>117</v>
+        <v>525</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>79</v>
@@ -24451,25 +24464,25 @@
         <v>80</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ184" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK184" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL184" t="s" s="2">
-        <v>78</v>
+        <v>533</v>
       </c>
       <c r="AM184" t="s" s="2">
-        <v>78</v>
+        <v>534</v>
       </c>
       <c r="AN184" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO184" t="s" s="2">
-        <v>78</v>
+        <v>535</v>
       </c>
     </row>
     <row r="185" hidden="true">
@@ -24477,7 +24490,7 @@
         <v>658</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -24485,7 +24498,7 @@
       </c>
       <c r="E185" s="2"/>
       <c r="F185" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G185" t="s" s="2">
         <v>89</v>
@@ -24500,24 +24513,22 @@
         <v>78</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>136</v>
+        <v>103</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>223</v>
+        <v>104</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N185" s="2"/>
       <c r="O185" s="2"/>
       <c r="P185" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q185" s="2"/>
       <c r="R185" t="s" s="2">
-        <v>555</v>
+        <v>78</v>
       </c>
       <c r="S185" t="s" s="2">
         <v>78</v>
@@ -24559,10 +24570,10 @@
         <v>78</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>89</v>
@@ -24580,7 +24591,7 @@
         <v>78</v>
       </c>
       <c r="AM185" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN185" t="s" s="2">
         <v>78</v>
@@ -24594,7 +24605,7 @@
         <v>659</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -24602,10 +24613,10 @@
       </c>
       <c r="E186" s="2"/>
       <c r="F186" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>78</v>
@@ -24617,13 +24628,13 @@
         <v>78</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>175</v>
+        <v>110</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>558</v>
+        <v>201</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" s="2"/>
@@ -24635,7 +24646,7 @@
         <v>78</v>
       </c>
       <c r="S186" t="s" s="2">
-        <v>651</v>
+        <v>78</v>
       </c>
       <c r="T186" t="s" s="2">
         <v>78</v>
@@ -24650,41 +24661,43 @@
         <v>78</v>
       </c>
       <c r="X186" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="Y186" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z186" t="s" s="2">
-        <v>559</v>
+        <v>78</v>
       </c>
       <c r="AA186" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB186" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC186" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD186" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE186" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>233</v>
+        <v>117</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ186" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK186" t="s" s="2">
         <v>78</v>
@@ -24693,7 +24706,7 @@
         <v>78</v>
       </c>
       <c r="AM186" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AN186" t="s" s="2">
         <v>78</v>
@@ -24707,18 +24720,20 @@
         <v>660</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="C187" s="2"/>
+        <v>543</v>
+      </c>
+      <c r="C187" t="s" s="2">
+        <v>545</v>
+      </c>
       <c r="D187" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E187" s="2"/>
       <c r="F187" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H187" t="s" s="2">
         <v>78</v>
@@ -24727,23 +24742,19 @@
         <v>78</v>
       </c>
       <c r="J187" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>153</v>
+        <v>546</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>395</v>
+        <v>547</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N187" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>398</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
         <v>78</v>
       </c>
@@ -24791,7 +24802,7 @@
         <v>78</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>399</v>
+        <v>117</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>79</v>
@@ -24803,16 +24814,16 @@
         <v>207</v>
       </c>
       <c r="AJ187" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK187" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL187" t="s" s="2">
-        <v>400</v>
+        <v>78</v>
       </c>
       <c r="AM187" t="s" s="2">
-        <v>401</v>
+        <v>78</v>
       </c>
       <c r="AN187" t="s" s="2">
         <v>78</v>
@@ -24826,7 +24837,7 @@
         <v>661</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>578</v>
+        <v>550</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -24840,29 +24851,25 @@
         <v>89</v>
       </c>
       <c r="H188" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J188" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K188" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>452</v>
+        <v>104</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N188" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N188" s="2"/>
+      <c r="O188" s="2"/>
       <c r="P188" t="s" s="2">
         <v>78</v>
       </c>
@@ -24910,7 +24917,7 @@
         <v>78</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>456</v>
+        <v>106</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>79</v>
@@ -24919,19 +24926,19 @@
         <v>89</v>
       </c>
       <c r="AI188" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ188" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK188" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL188" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="AM188" t="s" s="2">
-        <v>458</v>
+        <v>107</v>
       </c>
       <c r="AN188" t="s" s="2">
         <v>78</v>
@@ -24945,7 +24952,7 @@
         <v>662</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>662</v>
+        <v>552</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -24956,32 +24963,28 @@
         <v>79</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>663</v>
+        <v>200</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N189" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="O189" t="s" s="2">
-        <v>666</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N189" s="2"/>
+      <c r="O189" s="2"/>
       <c r="P189" t="s" s="2">
         <v>78</v>
       </c>
@@ -25017,43 +25020,43 @@
         <v>78</v>
       </c>
       <c r="AB189" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC189" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD189" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE189" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>662</v>
+        <v>117</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH189" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>304</v>
+        <v>207</v>
       </c>
       <c r="AJ189" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>667</v>
+        <v>78</v>
       </c>
       <c r="AL189" t="s" s="2">
-        <v>668</v>
+        <v>78</v>
       </c>
       <c r="AM189" t="s" s="2">
-        <v>669</v>
+        <v>78</v>
       </c>
       <c r="AN189" t="s" s="2">
-        <v>670</v>
+        <v>78</v>
       </c>
       <c r="AO189" t="s" s="2">
         <v>78</v>
@@ -25061,10 +25064,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>671</v>
+        <v>554</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -25072,13 +25075,13 @@
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>78</v>
@@ -25087,26 +25090,24 @@
         <v>78</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>103</v>
+        <v>136</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>672</v>
+        <v>223</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>673</v>
+        <v>224</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O190" t="s" s="2">
-        <v>675</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O190" s="2"/>
       <c r="P190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q190" s="2"/>
       <c r="R190" t="s" s="2">
-        <v>78</v>
+        <v>555</v>
       </c>
       <c r="S190" t="s" s="2">
         <v>78</v>
@@ -25148,28 +25149,28 @@
         <v>78</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>671</v>
+        <v>227</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ190" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK190" t="s" s="2">
-        <v>676</v>
+        <v>78</v>
       </c>
       <c r="AL190" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM190" t="s" s="2">
-        <v>669</v>
+        <v>198</v>
       </c>
       <c r="AN190" t="s" s="2">
         <v>78</v>
@@ -25180,10 +25181,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>677</v>
+        <v>557</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -25194,10 +25195,10 @@
         <v>79</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H191" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I191" t="s" s="2">
         <v>78</v>
@@ -25206,20 +25207,16 @@
         <v>78</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>678</v>
+        <v>175</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>679</v>
+        <v>231</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N191" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O191" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>558</v>
+      </c>
+      <c r="N191" s="2"/>
+      <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>78</v>
       </c>
@@ -25228,7 +25225,7 @@
         <v>78</v>
       </c>
       <c r="S191" t="s" s="2">
-        <v>78</v>
+        <v>656</v>
       </c>
       <c r="T191" t="s" s="2">
         <v>78</v>
@@ -25243,53 +25240,53 @@
         <v>78</v>
       </c>
       <c r="X191" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y191" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="Y191" s="2"/>
       <c r="Z191" t="s" s="2">
-        <v>78</v>
+        <v>559</v>
       </c>
       <c r="AA191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB191" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="AC191" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC191" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD191" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE191" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>677</v>
+        <v>233</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH191" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI191" t="s" s="2">
         <v>207</v>
       </c>
       <c r="AJ191" t="s" s="2">
-        <v>684</v>
+        <v>101</v>
       </c>
       <c r="AK191" t="s" s="2">
-        <v>685</v>
+        <v>78</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>686</v>
+        <v>78</v>
       </c>
       <c r="AM191" t="s" s="2">
-        <v>687</v>
+        <v>198</v>
       </c>
       <c r="AN191" t="s" s="2">
-        <v>688</v>
+        <v>78</v>
       </c>
       <c r="AO191" t="s" s="2">
         <v>78</v>
@@ -25297,10 +25294,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>689</v>
+        <v>561</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -25311,7 +25308,7 @@
         <v>79</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>78</v>
@@ -25320,19 +25317,23 @@
         <v>78</v>
       </c>
       <c r="J192" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>104</v>
+        <v>395</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N192" s="2"/>
-      <c r="O192" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P192" t="s" s="2">
         <v>78</v>
       </c>
@@ -25380,28 +25381,28 @@
         <v>78</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>106</v>
+        <v>399</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI192" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ192" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK192" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL192" t="s" s="2">
-        <v>78</v>
+        <v>400</v>
       </c>
       <c r="AM192" t="s" s="2">
-        <v>107</v>
+        <v>401</v>
       </c>
       <c r="AN192" t="s" s="2">
         <v>78</v>
@@ -25412,44 +25413,46 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>690</v>
+        <v>578</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E193" s="2"/>
       <c r="F193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J193" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>111</v>
+        <v>452</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>112</v>
+        <v>453</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O193" s="2"/>
+        <v>454</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="P193" t="s" s="2">
         <v>78</v>
       </c>
@@ -25485,40 +25488,40 @@
         <v>78</v>
       </c>
       <c r="AB193" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC193" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE193" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>117</v>
+        <v>456</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH193" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ193" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK193" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL193" t="s" s="2">
-        <v>78</v>
+        <v>457</v>
       </c>
       <c r="AM193" t="s" s="2">
-        <v>107</v>
+        <v>458</v>
       </c>
       <c r="AN193" t="s" s="2">
         <v>78</v>
@@ -25529,14 +25532,12 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>691</v>
+        <v>667</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>690</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>692</v>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25548,25 +25549,29 @@
         <v>89</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>693</v>
+        <v>103</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>694</v>
+        <v>668</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N194" s="2"/>
-      <c r="O194" s="2"/>
+        <v>669</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="P194" t="s" s="2">
         <v>78</v>
       </c>
@@ -25614,31 +25619,31 @@
         <v>78</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>117</v>
+        <v>667</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>78</v>
+        <v>304</v>
       </c>
       <c r="AJ194" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>78</v>
+        <v>672</v>
       </c>
       <c r="AL194" t="s" s="2">
-        <v>78</v>
+        <v>673</v>
       </c>
       <c r="AM194" t="s" s="2">
-        <v>78</v>
+        <v>674</v>
       </c>
       <c r="AN194" t="s" s="2">
-        <v>78</v>
+        <v>675</v>
       </c>
       <c r="AO194" t="s" s="2">
         <v>78</v>
@@ -25646,10 +25651,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -25657,31 +25662,35 @@
       </c>
       <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G195" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H195" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I195" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J195" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>697</v>
+        <v>677</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="N195" s="2"/>
-      <c r="O195" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="N195" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="O195" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="P195" t="s" s="2">
         <v>78</v>
       </c>
@@ -25705,13 +25714,13 @@
         <v>78</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>324</v>
+        <v>78</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>699</v>
+        <v>78</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>700</v>
+        <v>78</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>78</v>
@@ -25729,31 +25738,31 @@
         <v>78</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>701</v>
+        <v>676</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI195" t="s" s="2">
-        <v>702</v>
+        <v>78</v>
       </c>
       <c r="AJ195" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK195" t="s" s="2">
-        <v>78</v>
+        <v>681</v>
       </c>
       <c r="AL195" t="s" s="2">
-        <v>703</v>
+        <v>78</v>
       </c>
       <c r="AM195" t="s" s="2">
-        <v>704</v>
+        <v>674</v>
       </c>
       <c r="AN195" t="s" s="2">
-        <v>705</v>
+        <v>78</v>
       </c>
       <c r="AO195" t="s" s="2">
         <v>78</v>
@@ -25761,10 +25770,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>706</v>
+        <v>682</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -25772,34 +25781,34 @@
       </c>
       <c r="E196" s="2"/>
       <c r="F196" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H196" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J196" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>103</v>
+        <v>683</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>707</v>
+        <v>684</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>708</v>
+        <v>685</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>709</v>
+        <v>686</v>
       </c>
       <c r="O196" t="s" s="2">
-        <v>710</v>
+        <v>687</v>
       </c>
       <c r="P196" t="s" s="2">
         <v>78</v>
@@ -25836,43 +25845,41 @@
         <v>78</v>
       </c>
       <c r="AB196" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC196" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>688</v>
+      </c>
+      <c r="AC196" s="2"/>
       <c r="AD196" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE196" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>711</v>
+        <v>682</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI196" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ196" t="s" s="2">
-        <v>101</v>
+        <v>689</v>
       </c>
       <c r="AK196" t="s" s="2">
-        <v>78</v>
+        <v>690</v>
       </c>
       <c r="AL196" t="s" s="2">
-        <v>712</v>
+        <v>691</v>
       </c>
       <c r="AM196" t="s" s="2">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="AN196" t="s" s="2">
-        <v>362</v>
+        <v>693</v>
       </c>
       <c r="AO196" t="s" s="2">
         <v>78</v>
@@ -25880,10 +25887,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>714</v>
+        <v>694</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -25900,26 +25907,22 @@
         <v>78</v>
       </c>
       <c r="I197" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J197" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>175</v>
+        <v>103</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>715</v>
+        <v>104</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="N197" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="O197" t="s" s="2">
-        <v>718</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N197" s="2"/>
+      <c r="O197" s="2"/>
       <c r="P197" t="s" s="2">
         <v>78</v>
       </c>
@@ -25943,13 +25946,13 @@
         <v>78</v>
       </c>
       <c r="X197" t="s" s="2">
-        <v>324</v>
+        <v>78</v>
       </c>
       <c r="Y197" t="s" s="2">
-        <v>719</v>
+        <v>78</v>
       </c>
       <c r="Z197" t="s" s="2">
-        <v>720</v>
+        <v>78</v>
       </c>
       <c r="AA197" t="s" s="2">
         <v>78</v>
@@ -25967,7 +25970,7 @@
         <v>78</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>721</v>
+        <v>106</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>79</v>
@@ -25979,19 +25982,19 @@
         <v>78</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL197" t="s" s="2">
-        <v>722</v>
+        <v>78</v>
       </c>
       <c r="AM197" t="s" s="2">
-        <v>723</v>
+        <v>107</v>
       </c>
       <c r="AN197" t="s" s="2">
-        <v>724</v>
+        <v>78</v>
       </c>
       <c r="AO197" t="s" s="2">
         <v>78</v>
@@ -25999,21 +26002,21 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>725</v>
+        <v>695</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G198" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H198" t="s" s="2">
         <v>78</v>
@@ -26022,19 +26025,19 @@
         <v>78</v>
       </c>
       <c r="J198" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>726</v>
+        <v>110</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>727</v>
+        <v>111</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>728</v>
+        <v>112</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>729</v>
+        <v>113</v>
       </c>
       <c r="O198" s="2"/>
       <c r="P198" t="s" s="2">
@@ -26072,37 +26075,37 @@
         <v>78</v>
       </c>
       <c r="AB198" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC198" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD198" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE198" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>730</v>
+        <v>117</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH198" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI198" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>107</v>
@@ -26116,12 +26119,14 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>731</v>
+        <v>696</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C199" s="2"/>
+        <v>695</v>
+      </c>
+      <c r="C199" t="s" s="2">
+        <v>697</v>
+      </c>
       <c r="D199" t="s" s="2">
         <v>78</v>
       </c>
@@ -26139,16 +26144,16 @@
         <v>78</v>
       </c>
       <c r="J199" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>230</v>
+        <v>698</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>732</v>
+        <v>699</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>733</v>
+        <v>700</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -26199,31 +26204,31 @@
         <v>78</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>734</v>
+        <v>117</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH199" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI199" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ199" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK199" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL199" t="s" s="2">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="AM199" t="s" s="2">
-        <v>735</v>
+        <v>78</v>
       </c>
       <c r="AN199" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AO199" t="s" s="2">
         <v>78</v>
@@ -26231,23 +26236,21 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>736</v>
+        <v>701</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C200" t="s" s="2">
-        <v>737</v>
-      </c>
+        <v>701</v>
+      </c>
+      <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E200" s="2"/>
       <c r="F200" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G200" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H200" t="s" s="2">
         <v>78</v>
@@ -26256,23 +26259,19 @@
         <v>78</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>738</v>
+        <v>175</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>739</v>
+        <v>702</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N200" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O200" t="s" s="2">
-        <v>682</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
       <c r="P200" t="s" s="2">
         <v>78</v>
       </c>
@@ -26296,13 +26295,13 @@
         <v>78</v>
       </c>
       <c r="X200" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="Y200" t="s" s="2">
-        <v>78</v>
+        <v>704</v>
       </c>
       <c r="Z200" t="s" s="2">
-        <v>78</v>
+        <v>705</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>78</v>
@@ -26320,31 +26319,31 @@
         <v>78</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH200" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI200" t="s" s="2">
-        <v>207</v>
+        <v>707</v>
       </c>
       <c r="AJ200" t="s" s="2">
-        <v>684</v>
+        <v>101</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>740</v>
+        <v>78</v>
       </c>
       <c r="AL200" t="s" s="2">
-        <v>686</v>
+        <v>708</v>
       </c>
       <c r="AM200" t="s" s="2">
-        <v>687</v>
+        <v>709</v>
       </c>
       <c r="AN200" t="s" s="2">
-        <v>688</v>
+        <v>710</v>
       </c>
       <c r="AO200" t="s" s="2">
         <v>78</v>
@@ -26352,10 +26351,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>741</v>
+        <v>711</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>741</v>
+        <v>711</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -26363,34 +26362,34 @@
       </c>
       <c r="E201" s="2"/>
       <c r="F201" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G201" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H201" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I201" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J201" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I201" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J201" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K201" t="s" s="2">
-        <v>742</v>
+        <v>103</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>743</v>
+        <v>712</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>744</v>
+        <v>713</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>745</v>
+        <v>714</v>
       </c>
       <c r="O201" t="s" s="2">
-        <v>746</v>
+        <v>715</v>
       </c>
       <c r="P201" t="s" s="2">
         <v>78</v>
@@ -26439,31 +26438,31 @@
         <v>78</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>741</v>
+        <v>716</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH201" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ201" t="s" s="2">
-        <v>747</v>
+        <v>101</v>
       </c>
       <c r="AK201" t="s" s="2">
-        <v>748</v>
+        <v>78</v>
       </c>
       <c r="AL201" t="s" s="2">
-        <v>749</v>
+        <v>717</v>
       </c>
       <c r="AM201" t="s" s="2">
-        <v>750</v>
+        <v>718</v>
       </c>
       <c r="AN201" t="s" s="2">
-        <v>751</v>
+        <v>362</v>
       </c>
       <c r="AO201" t="s" s="2">
         <v>78</v>
@@ -26471,10 +26470,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>752</v>
+        <v>719</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -26491,23 +26490,25 @@
         <v>78</v>
       </c>
       <c r="I202" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="J202" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>753</v>
+        <v>175</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>754</v>
+        <v>720</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>755</v>
-      </c>
-      <c r="N202" s="2"/>
+        <v>721</v>
+      </c>
+      <c r="N202" t="s" s="2">
+        <v>722</v>
+      </c>
       <c r="O202" t="s" s="2">
-        <v>756</v>
+        <v>723</v>
       </c>
       <c r="P202" t="s" s="2">
         <v>78</v>
@@ -26532,13 +26533,13 @@
         <v>78</v>
       </c>
       <c r="X202" t="s" s="2">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>78</v>
+        <v>724</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>78</v>
+        <v>725</v>
       </c>
       <c r="AA202" t="s" s="2">
         <v>78</v>
@@ -26556,7 +26557,7 @@
         <v>78</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>752</v>
+        <v>726</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>79</v>
@@ -26574,13 +26575,13 @@
         <v>78</v>
       </c>
       <c r="AL202" t="s" s="2">
-        <v>521</v>
+        <v>727</v>
       </c>
       <c r="AM202" t="s" s="2">
-        <v>757</v>
+        <v>728</v>
       </c>
       <c r="AN202" t="s" s="2">
-        <v>107</v>
+        <v>729</v>
       </c>
       <c r="AO202" t="s" s="2">
         <v>78</v>
@@ -26588,10 +26589,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>758</v>
+        <v>730</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>758</v>
+        <v>730</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -26611,18 +26612,20 @@
         <v>78</v>
       </c>
       <c r="J203" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>103</v>
+        <v>731</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>104</v>
+        <v>732</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N203" s="2"/>
+        <v>733</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
         <v>78</v>
@@ -26671,7 +26674,7 @@
         <v>78</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>106</v>
+        <v>735</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>79</v>
@@ -26683,13 +26686,13 @@
         <v>78</v>
       </c>
       <c r="AJ203" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK203" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL203" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AM203" t="s" s="2">
         <v>107</v>
@@ -26703,21 +26706,21 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>759</v>
+        <v>736</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>78</v>
@@ -26726,20 +26729,18 @@
         <v>78</v>
       </c>
       <c r="J204" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>110</v>
+        <v>230</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>111</v>
+        <v>737</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>738</v>
+      </c>
+      <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
         <v>78</v>
@@ -26776,43 +26777,43 @@
         <v>78</v>
       </c>
       <c r="AB204" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC204" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE204" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>117</v>
+        <v>739</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ204" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK204" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL204" t="s" s="2">
-        <v>78</v>
+        <v>198</v>
       </c>
       <c r="AM204" t="s" s="2">
-        <v>107</v>
+        <v>740</v>
       </c>
       <c r="AN204" t="s" s="2">
-        <v>78</v>
+        <v>370</v>
       </c>
       <c r="AO204" t="s" s="2">
         <v>78</v>
@@ -26820,12 +26821,14 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="C205" s="2"/>
+        <v>682</v>
+      </c>
+      <c r="C205" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="D205" t="s" s="2">
         <v>78</v>
       </c>
@@ -26834,7 +26837,7 @@
         <v>79</v>
       </c>
       <c r="G205" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H205" t="s" s="2">
         <v>78</v>
@@ -26843,21 +26846,23 @@
         <v>78</v>
       </c>
       <c r="J205" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>103</v>
+        <v>743</v>
       </c>
       <c r="L205" t="s" s="2">
-        <v>761</v>
+        <v>744</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>762</v>
+        <v>685</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="O205" s="2"/>
+        <v>686</v>
+      </c>
+      <c r="O205" t="s" s="2">
+        <v>687</v>
+      </c>
       <c r="P205" t="s" s="2">
         <v>78</v>
       </c>
@@ -26905,31 +26910,31 @@
         <v>78</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>764</v>
+        <v>682</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH205" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI205" t="s" s="2">
-        <v>765</v>
+        <v>207</v>
       </c>
       <c r="AJ205" t="s" s="2">
-        <v>101</v>
+        <v>689</v>
       </c>
       <c r="AK205" t="s" s="2">
-        <v>78</v>
+        <v>745</v>
       </c>
       <c r="AL205" t="s" s="2">
-        <v>78</v>
+        <v>691</v>
       </c>
       <c r="AM205" t="s" s="2">
-        <v>198</v>
+        <v>692</v>
       </c>
       <c r="AN205" t="s" s="2">
-        <v>78</v>
+        <v>693</v>
       </c>
       <c r="AO205" t="s" s="2">
         <v>78</v>
@@ -26937,10 +26942,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>766</v>
+        <v>746</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -26951,30 +26956,32 @@
         <v>79</v>
       </c>
       <c r="G206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H206" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I206" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J206" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>136</v>
+        <v>747</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>769</v>
-      </c>
-      <c r="O206" s="2"/>
+        <v>750</v>
+      </c>
+      <c r="O206" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="P206" t="s" s="2">
         <v>78</v>
       </c>
@@ -26998,11 +27005,13 @@
         <v>78</v>
       </c>
       <c r="X206" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Y206" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="Y206" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="Z206" t="s" s="2">
-        <v>539</v>
+        <v>78</v>
       </c>
       <c r="AA206" t="s" s="2">
         <v>78</v>
@@ -27020,31 +27029,31 @@
         <v>78</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>770</v>
+        <v>746</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH206" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI206" t="s" s="2">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="AJ206" t="s" s="2">
-        <v>101</v>
+        <v>752</v>
       </c>
       <c r="AK206" t="s" s="2">
-        <v>78</v>
+        <v>753</v>
       </c>
       <c r="AL206" t="s" s="2">
-        <v>78</v>
+        <v>754</v>
       </c>
       <c r="AM206" t="s" s="2">
-        <v>198</v>
+        <v>755</v>
       </c>
       <c r="AN206" t="s" s="2">
-        <v>78</v>
+        <v>756</v>
       </c>
       <c r="AO206" t="s" s="2">
         <v>78</v>
@@ -27052,10 +27061,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>771</v>
+        <v>757</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -27078,18 +27087,18 @@
         <v>90</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>298</v>
+        <v>758</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>772</v>
+        <v>759</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>774</v>
-      </c>
-      <c r="O207" s="2"/>
+        <v>760</v>
+      </c>
+      <c r="N207" s="2"/>
+      <c r="O207" t="s" s="2">
+        <v>761</v>
+      </c>
       <c r="P207" t="s" s="2">
         <v>78</v>
       </c>
@@ -27137,7 +27146,7 @@
         <v>78</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>775</v>
+        <v>757</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>79</v>
@@ -27155,13 +27164,13 @@
         <v>78</v>
       </c>
       <c r="AL207" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="AM207" t="s" s="2">
-        <v>776</v>
+        <v>762</v>
       </c>
       <c r="AN207" t="s" s="2">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="AO207" t="s" s="2">
         <v>78</v>
@@ -27169,10 +27178,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>777</v>
+        <v>763</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -27192,20 +27201,18 @@
         <v>78</v>
       </c>
       <c r="J208" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K208" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>778</v>
+        <v>104</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>780</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N208" s="2"/>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
         <v>78</v>
@@ -27254,7 +27261,7 @@
         <v>78</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>781</v>
+        <v>106</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>79</v>
@@ -27266,7 +27273,7 @@
         <v>78</v>
       </c>
       <c r="AJ208" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK208" t="s" s="2">
         <v>78</v>
@@ -27275,7 +27282,7 @@
         <v>78</v>
       </c>
       <c r="AM208" t="s" s="2">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="AN208" t="s" s="2">
         <v>78</v>
@@ -27286,14 +27293,14 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>782</v>
+        <v>764</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E209" s="2"/>
       <c r="F209" t="s" s="2">
@@ -27312,20 +27319,18 @@
         <v>78</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>783</v>
+        <v>110</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>784</v>
+        <v>111</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>785</v>
+        <v>112</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>787</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
         <v>78</v>
       </c>
@@ -27361,19 +27366,19 @@
         <v>78</v>
       </c>
       <c r="AB209" t="s" s="2">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AD209" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE209" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>782</v>
+        <v>117</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>79</v>
@@ -27385,7 +27390,7 @@
         <v>78</v>
       </c>
       <c r="AJ209" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK209" t="s" s="2">
         <v>78</v>
@@ -27394,7 +27399,7 @@
         <v>78</v>
       </c>
       <c r="AM209" t="s" s="2">
-        <v>788</v>
+        <v>107</v>
       </c>
       <c r="AN209" t="s" s="2">
         <v>78</v>
@@ -27405,10 +27410,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>789</v>
+        <v>765</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -27428,18 +27433,20 @@
         <v>78</v>
       </c>
       <c r="J210" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K210" t="s" s="2">
         <v>103</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>104</v>
+        <v>766</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N210" s="2"/>
+        <v>767</v>
+      </c>
+      <c r="N210" t="s" s="2">
+        <v>768</v>
+      </c>
       <c r="O210" s="2"/>
       <c r="P210" t="s" s="2">
         <v>78</v>
@@ -27488,7 +27495,7 @@
         <v>78</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>106</v>
+        <v>769</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>79</v>
@@ -27497,10 +27504,10 @@
         <v>89</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>78</v>
+        <v>770</v>
       </c>
       <c r="AJ210" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK210" t="s" s="2">
         <v>78</v>
@@ -27509,7 +27516,7 @@
         <v>78</v>
       </c>
       <c r="AM210" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN210" t="s" s="2">
         <v>78</v>
@@ -27520,21 +27527,21 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E211" s="2"/>
       <c r="F211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>78</v>
@@ -27543,19 +27550,19 @@
         <v>78</v>
       </c>
       <c r="J211" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>111</v>
+        <v>772</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>112</v>
+        <v>773</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>113</v>
+        <v>774</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -27581,13 +27588,11 @@
         <v>78</v>
       </c>
       <c r="X211" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y211" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="Y211" s="2"/>
       <c r="Z211" t="s" s="2">
-        <v>78</v>
+        <v>539</v>
       </c>
       <c r="AA211" t="s" s="2">
         <v>78</v>
@@ -27605,19 +27610,19 @@
         <v>78</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>117</v>
+        <v>775</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH211" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI211" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ211" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK211" t="s" s="2">
         <v>78</v>
@@ -27626,7 +27631,7 @@
         <v>78</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>107</v>
+        <v>198</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>78</v>
@@ -27637,46 +27642,44 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
-        <v>792</v>
+        <v>78</v>
       </c>
       <c r="E212" s="2"/>
       <c r="F212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I212" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J212" t="s" s="2">
         <v>90</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>110</v>
+        <v>298</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>794</v>
+        <v>778</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O212" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>779</v>
+      </c>
+      <c r="O212" s="2"/>
       <c r="P212" t="s" s="2">
         <v>78</v>
       </c>
@@ -27724,19 +27727,19 @@
         <v>78</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI212" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ212" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK212" t="s" s="2">
         <v>78</v>
@@ -27745,7 +27748,7 @@
         <v>78</v>
       </c>
       <c r="AM212" t="s" s="2">
-        <v>198</v>
+        <v>781</v>
       </c>
       <c r="AN212" t="s" s="2">
         <v>78</v>
@@ -27756,10 +27759,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>796</v>
+        <v>782</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -27779,21 +27782,21 @@
         <v>78</v>
       </c>
       <c r="J213" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>331</v>
+        <v>103</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>797</v>
+        <v>783</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="N213" s="2"/>
-      <c r="O213" t="s" s="2">
-        <v>799</v>
-      </c>
+        <v>784</v>
+      </c>
+      <c r="N213" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="O213" s="2"/>
       <c r="P213" t="s" s="2">
         <v>78</v>
       </c>
@@ -27817,13 +27820,13 @@
         <v>78</v>
       </c>
       <c r="X213" t="s" s="2">
-        <v>157</v>
+        <v>78</v>
       </c>
       <c r="Y213" t="s" s="2">
-        <v>800</v>
+        <v>78</v>
       </c>
       <c r="Z213" t="s" s="2">
-        <v>801</v>
+        <v>78</v>
       </c>
       <c r="AA213" t="s" s="2">
         <v>78</v>
@@ -27841,7 +27844,7 @@
         <v>78</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>796</v>
+        <v>786</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>79</v>
@@ -27862,7 +27865,7 @@
         <v>78</v>
       </c>
       <c r="AM213" t="s" s="2">
-        <v>802</v>
+        <v>198</v>
       </c>
       <c r="AN213" t="s" s="2">
         <v>78</v>
@@ -27873,10 +27876,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -27887,7 +27890,7 @@
         <v>79</v>
       </c>
       <c r="G214" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H214" t="s" s="2">
         <v>78</v>
@@ -27899,17 +27902,19 @@
         <v>78</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>804</v>
+        <v>788</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="M214" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="N214" s="2"/>
+        <v>790</v>
+      </c>
+      <c r="N214" t="s" s="2">
+        <v>791</v>
+      </c>
       <c r="O214" t="s" s="2">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="P214" t="s" s="2">
         <v>78</v>
@@ -27958,13 +27963,13 @@
         <v>78</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>803</v>
+        <v>787</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH214" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI214" t="s" s="2">
         <v>78</v>
@@ -27976,10 +27981,10 @@
         <v>78</v>
       </c>
       <c r="AL214" t="s" s="2">
-        <v>808</v>
+        <v>78</v>
       </c>
       <c r="AM214" t="s" s="2">
-        <v>809</v>
+        <v>793</v>
       </c>
       <c r="AN214" t="s" s="2">
         <v>78</v>
@@ -27990,10 +27995,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>810</v>
+        <v>794</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -28004,7 +28009,7 @@
         <v>79</v>
       </c>
       <c r="G215" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H215" t="s" s="2">
         <v>78</v>
@@ -28016,18 +28021,16 @@
         <v>78</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>678</v>
+        <v>103</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>811</v>
+        <v>104</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>680</v>
+        <v>105</v>
       </c>
       <c r="N215" s="2"/>
-      <c r="O215" t="s" s="2">
-        <v>812</v>
-      </c>
+      <c r="O215" s="2"/>
       <c r="P215" t="s" s="2">
         <v>78</v>
       </c>
@@ -28075,31 +28078,31 @@
         <v>78</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>810</v>
+        <v>106</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH215" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI215" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ215" t="s" s="2">
-        <v>813</v>
+        <v>78</v>
       </c>
       <c r="AK215" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL215" t="s" s="2">
-        <v>686</v>
+        <v>78</v>
       </c>
       <c r="AM215" t="s" s="2">
-        <v>687</v>
+        <v>107</v>
       </c>
       <c r="AN215" t="s" s="2">
-        <v>688</v>
+        <v>78</v>
       </c>
       <c r="AO215" t="s" s="2">
         <v>78</v>
@@ -28107,21 +28110,21 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="E216" s="2"/>
       <c r="F216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G216" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H216" t="s" s="2">
         <v>78</v>
@@ -28133,20 +28136,18 @@
         <v>78</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>815</v>
+        <v>110</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>816</v>
+        <v>111</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>744</v>
+        <v>112</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>745</v>
-      </c>
-      <c r="O216" t="s" s="2">
-        <v>817</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O216" s="2"/>
       <c r="P216" t="s" s="2">
         <v>78</v>
       </c>
@@ -28194,31 +28195,31 @@
         <v>78</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>814</v>
+        <v>117</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH216" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="AJ216" t="s" s="2">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="AK216" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL216" t="s" s="2">
-        <v>749</v>
+        <v>78</v>
       </c>
       <c r="AM216" t="s" s="2">
-        <v>750</v>
+        <v>107</v>
       </c>
       <c r="AN216" t="s" s="2">
-        <v>751</v>
+        <v>78</v>
       </c>
       <c r="AO216" t="s" s="2">
         <v>78</v>
@@ -28226,14 +28227,14 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>818</v>
+        <v>796</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
-        <v>78</v>
+        <v>797</v>
       </c>
       <c r="E217" s="2"/>
       <c r="F217" t="s" s="2">
@@ -28243,26 +28244,28 @@
         <v>80</v>
       </c>
       <c r="H217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I217" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I217" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="J217" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>819</v>
+        <v>110</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>820</v>
+        <v>798</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="N217" s="2"/>
+        <v>799</v>
+      </c>
+      <c r="N217" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O217" t="s" s="2">
-        <v>822</v>
+        <v>295</v>
       </c>
       <c r="P217" t="s" s="2">
         <v>78</v>
@@ -28311,7 +28314,7 @@
         <v>78</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>79</v>
@@ -28323,26 +28326,613 @@
         <v>78</v>
       </c>
       <c r="AJ217" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AK217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM217" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN217" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO217" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="218" hidden="true">
+      <c r="A218" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="B218" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="C218" s="2"/>
+      <c r="D218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E218" s="2"/>
+      <c r="F218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G218" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K218" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="L218" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M218" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="N218" s="2"/>
+      <c r="O218" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="P218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q218" s="2"/>
+      <c r="R218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X218" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="Y218" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="Z218" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="AA218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF218" t="s" s="2">
+        <v>801</v>
+      </c>
+      <c r="AG218" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH218" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ218" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM217" t="s" s="2">
+      <c r="AK218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM218" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="AN218" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO218" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="219" hidden="true">
+      <c r="A219" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="B219" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="C219" s="2"/>
+      <c r="D219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E219" s="2"/>
+      <c r="F219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G219" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K219" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="L219" t="s" s="2">
+        <v>810</v>
+      </c>
+      <c r="M219" t="s" s="2">
+        <v>811</v>
+      </c>
+      <c r="N219" s="2"/>
+      <c r="O219" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="P219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q219" s="2"/>
+      <c r="R219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF219" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="AG219" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH219" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ219" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL219" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="AM219" t="s" s="2">
+        <v>814</v>
+      </c>
+      <c r="AN219" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO219" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="220" hidden="true">
+      <c r="A220" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="B220" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="C220" s="2"/>
+      <c r="D220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E220" s="2"/>
+      <c r="F220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K220" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="M220" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N220" s="2"/>
+      <c r="O220" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="P220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q220" s="2"/>
+      <c r="R220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF220" t="s" s="2">
+        <v>815</v>
+      </c>
+      <c r="AG220" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH220" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI220" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AJ220" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="AK220" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL220" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="AM220" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AN220" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="AO220" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="221" hidden="true">
+      <c r="A221" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="B221" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="C221" s="2"/>
+      <c r="D221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E221" s="2"/>
+      <c r="F221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G221" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K221" t="s" s="2">
+        <v>820</v>
+      </c>
+      <c r="L221" t="s" s="2">
+        <v>821</v>
+      </c>
+      <c r="M221" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="N221" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>822</v>
+      </c>
+      <c r="P221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q221" s="2"/>
+      <c r="R221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF221" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="AG221" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH221" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI221" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AJ221" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK221" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL221" t="s" s="2">
+        <v>754</v>
+      </c>
+      <c r="AM221" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="AN221" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="AO221" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="222" hidden="true">
+      <c r="A222" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="B222" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="C222" s="2"/>
+      <c r="D222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E222" s="2"/>
+      <c r="F222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H222" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K222" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="L222" t="s" s="2">
+        <v>825</v>
+      </c>
+      <c r="M222" t="s" s="2">
+        <v>826</v>
+      </c>
+      <c r="N222" s="2"/>
+      <c r="O222" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="P222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q222" s="2"/>
+      <c r="R222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF222" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="AG222" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH222" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ222" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM222" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="AN217" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO217" t="s" s="2">
+      <c r="AN222" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO222" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO217">
+  <autoFilter ref="A1:AO222">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -28352,7 +28942,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI216">
+  <conditionalFormatting sqref="A2:AI221">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T11:51:09+00:00</t>
+    <t>2024-07-02T12:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:01:26+00:00</t>
+    <t>2024-07-02T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T12:28:16+00:00</t>
+    <t>2024-07-02T14:06:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T14:06:23+00:00</t>
+    <t>2024-07-09T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
+++ b/110-creation-exemples/ig/StructureDefinition-as-dr-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T09:28:43+00:00</t>
+    <t>2024-07-09T09:35:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
